--- a/data/nfm_merge.xlsx
+++ b/data/nfm_merge.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L119"/>
+  <dimension ref="A1:P119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,17 +464,37 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>국적/시대</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>용도/기능</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>크기</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>seq</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>image_url</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>image_urls</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>seq</t>
         </is>
       </c>
     </row>
@@ -494,8 +514,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>5080</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -520,19 +542,31 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8271936.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8271936.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>가로 : 26 세로 : 26.7</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>조선시대 무관 중 당상관이 평상복의 앞뒤에 붙여 품계를 나타내던 표지. 청녹색 비단 바탕에 태극을 사이에 두고 대칭으로 서 있는 두 마리의 호랑이가 징금수로 놓여짐. 배경은 오색 구름으로 채워지고 하단에는 바위와 산, 물방울 등이 표현됨. 가장자리는 금사(金絲)로 구획됨. 뒷면에는 종이를 덧대고 홈질됨.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>PS0100200100100508000000</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -550,8 +584,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>5081</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5081</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -576,19 +612,31 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8271947.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8271947.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>세로 : 21.5 가로 : 20</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>조선시대 무관 중 당하관이 평상복의 앞뒤에 붙여 품계를 나타내던 표지. 청녹색 비단 바탕에 구름을 배경으로 흰색 호랑이가 앉아 있는 모습이 징금수로 놓여짐. 화면 하단에는 바위와 산, 물결과 물방울 등이 표현됨. 뒷면에는 종이를 덧대고 박음질됨.</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>PS0100200100100508100000</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -606,8 +654,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>29184</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>29184</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -632,19 +682,31 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8338170.do</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8338170.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>세로 : 20.7 가로 : 20.6</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>조선 시대에 문무관(文武官)이 입는 관복의 가슴과 등에 학이나 범을 수 놓아 붙이던 사각형의 표장(表章). 검정색 종이 바탕에 두 마리의 학이 날개를 활짝 편 상태로 구름과 함께 그려진 쌍학(雙鶴) 흉배임. 테두리는 초록색을 칠하여 두르고, 앞·뒷면 가장자리에 빨간색 종이를 둘러 붙였음. 왼쪽 테두리 부분에 자주색 꼰실이 끼워져 있음.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>PS0100200100102918400000</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -662,15 +724,21 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>915</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>웅비(熊비)흉배</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>웅비흉배</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>熊비</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
@@ -684,19 +752,31 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8286812.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8286812.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>세로 : 17 가로 : 16.2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>무관 3품이 사용하던 흉배의 재현품. 초록색 바탕에 은사로 수를 놓음. 웅비 2마리가 아래위로 마주보는 형상임. 웅비의 주위는 구름 문양으로 장식됨.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>PS0100200100900091500000</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -714,15 +794,21 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>914</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>노사(鷺사)흉배</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>노사흉배</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>鷺사</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
@@ -736,19 +822,31 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8402624.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8402624.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>가로 : 30 세로 : 30.5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>문관 6품이 사용하던 흉배의 재현품. 초록색 바탕에 금색 계열의 실로 수를 놓음. 가운데에 양날개를 편 노사(해오라기)가 한쪽 다리를 들고 바위 위에 서 있는 형태임. 바위, 물결, 불로초 형태의 구름 등으로 장식됨.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>PS0100200100900091400000</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -766,15 +864,21 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>916</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>백한(白鷳)흉배</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>백한흉배</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>白鷳</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
@@ -788,19 +892,31 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8292438.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8292438.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>가로 : 34 세로 : 34</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>문관 3품이 사용하던 흉배의 재현품. 바탕은 청색계열이며 미색의 실로 수를 놓음. 백한이 한쪽 다리를 들고 날개를 펴고 있는 형상임. 꼬리는 5갈래로 나뉘어 펼쳐져 있음. 백한을 중심으로 상단에는 구름을 하단에는 바위와 물결문양을 배치하여 장식함.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>PS0100200100900091600000</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -818,15 +934,21 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>917</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>해치(獬豸)흉배</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>해치흉배</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>獬豸</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
@@ -840,19 +962,31 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8402521.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8402521.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>가로 : 35.5 세로 : 36.5</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>대사헌(종2품)이 사용하던 흉배의 재현품. 바탕은 초록색이며 청색 ·분홍색 등의 실로 수놓음. 해치는 머리 한가운데 1개의 뿔이 있고, 꼬리끝에 긴털을 가진 신수(神獸)임. 해치 주위에는 구름이 가득하고 꽃과 불로초, 파도 등을 배치하여 장식함.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>PS0100200100900091700000</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -870,8 +1004,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>95917</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>95917</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -896,19 +1032,31 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8485330.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8485330.do; https://www.nfm.go.kr/common/apiimage/relic/8485331.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>가로 : 22.2 세로 : 24.8</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>문무백관의 관복(官服) 가슴과 등에 부착하여 품계(品階)를 나타내는 표지(標識). 직사각 형태. 쌍학, 구름, 바위 문양 등이 수(繡) 놓임. 뒷면에 나무판이 부착됨.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>PS0100200100109591700000</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -926,8 +1074,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>95918</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>95918</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -952,19 +1102,31 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8485338.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8485338.do; https://www.nfm.go.kr/common/apiimage/relic/8485339.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>가로 : 21.6 세로 : 22.8</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>문무백관의 관복(官服) 가슴과 등에 부착하여 품계(品階)를 나타내는 표지(標識). 직사각 형태. 쌍학, 구름, 바위 문양 등이 수(繡) 놓임. 뒷면 천으로 배접됨. 내부에 심이 들어 있음.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>PS0100200100109591800000</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -982,8 +1144,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>1026</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1008,19 +1172,31 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8273809.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8273809.do; https://www.nfm.go.kr/common/apiimage/relic/8273808.do; https://www.nfm.go.kr/common/apiimage/relic/8273807.do; https://www.nfm.go.kr/common/apiimage/relic/8273810.do; https://www.nfm.go.kr/common/apiimage/relic/8273811.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>가로 : 17.5 세로 : 19.2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>조선시대 문관 중 당하관(堂下官)이 평상복의 앞뒤에 붙여 품계를 나타내던 표지. 청색 비단 바탕에 영지를 물고 구름 속을 날아가는 학이 징금수로 놓여짐. 화면 하단에는 괴석과 파도문 등이 표현됨. 뒷면은 종이로 배접됨.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>PS0100200100100102600000</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1038,8 +1214,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>1935</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1935</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1064,19 +1242,31 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8269349.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8269349.do; https://www.nfm.go.kr/common/apiimage/relic/8269350.do; https://www.nfm.go.kr/common/apiimage/relic/8269352.do; https://www.nfm.go.kr/common/apiimage/relic/8269351.do; https://www.nfm.go.kr/common/apiimage/relic/8269353.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>가로 : 18.5 세로 : 20</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>조선시대 문관 중 당상관(堂上官)이 평상복의 앞뒤에 붙여 품계를 나타내던 표지. 청색 비단 바탕에 오색구름 속을 날아가는 두 마리의 학이 징금수로 놓여짐. 가장자리는 금사(金絲)로 구획됨.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>PS0100200100100193500000</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1094,8 +1284,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2033</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1120,19 +1312,31 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8536053.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8536053.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>세로 : 17 가로 : 16.2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>조선시대 문관 중 당상관(堂上官)이 평상복의 앞뒤에 붙여 품계를 나타내던 표지. 청색 비단 바탕에 영지를 물고 구름 속을 날아가는 두마리의 학이 은사(銀絲)로 수놓여짐. 화면 하단은 바위와 파도문 등이 표현됨. 뒷면은 종이로 배접됨.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>PS0100200100100203300000</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1150,8 +1354,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>2066</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2066</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1176,19 +1382,31 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8273837.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8273837.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>가로 : 20 세로 : 21</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>조선시대 문관 중 당하관이 평상복의 앞뒤에 붙여 품계를 나타내던 표지. 청녹색 비단 바탕에 영지를 물고 오색구름 속을 날아가는 학이 징금수로 놓여짐. 뒷면은 종이로 배접됨.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>PS0100200100100206600000</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1206,8 +1424,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>2082</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2082</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1232,19 +1452,31 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8557604.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8557604.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>가로 : 24 세로 : 25</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>조선시대 문관 중 당상관(堂上官)이 평상복의 앞뒤에 붙여 품계를 나타내던 표지. 청색 비단 바탕에 영지를 물고 구름 속을 날아가는 학이 징금수로 놓여짐. 화면 하단은 바위와 산, 물방울 등이 표현됨. 뒷면은 종이로 배접됨.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>PS0100200100100208200000</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1262,8 +1494,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>4205</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4205</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1288,19 +1522,31 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8299462.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8299462.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>가로 : 17.5 세로 : 19</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>文官 堂上官 着用. 卍字紋. 조선시대 문관 중 당상관(堂上官)이 평상복의 앞뒤에 붙여 품계를 나타내던 표지. 청녹색 비단 바탕에 불로초를 물고 구름 속을 날아가는 두 마리의 학이 징금수로 놓여짐. 화면 하단에는 바위와 산, 물결 등이 표현됨. 뒷면은 청녹색 명주로 배접됨.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>PS0100200100100420500000</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1318,8 +1564,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>63779</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>63779</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1344,19 +1592,31 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8239575.do</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8239575.do; https://www.nfm.go.kr/common/apiimage/relic/8239576.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>가로 : 17.5 세로 : 19.7</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>문무백관 관복(官服)에 부착하여 품계(品階)를 나타내는 표장(表章). 직사각 형태. 쌍학, 파도, 구름무늬 등이 수(繡) 놓임. 뒷면은 한지로 배접됨.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
           <t>PS0100200100106377900000</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1374,8 +1634,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>77504</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>77504</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1400,19 +1662,31 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8565938.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8565938.do</t>
+          <t>의-의류-부분품-보/흉배 / 사회생활-의례생활-상장</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>너비 : 38 길이 : 37</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>문무백관 관복(官服)의 가슴과 등에 부착하여 품계(品階)를 나타내는 표장(表章). 통훈대부(通訓大夫) 홍씨 묘(경기도 남양주 별내면 화접리 5-2지점 묘232) 출토. 무문단(無紋段)으로 만들어짐. 정사각 형태. 해오라기, 파도, 구름무늬가 수(繡) 놓이고, 가장자리에 뇌(雷)무늬 장식이 둘려짐.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>PS0100200100107750400000</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1430,8 +1704,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>4204</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1456,19 +1732,31 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8244369.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8244369.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>가로 : 20.3 세로 : 22.5</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>文官 1 ∼ 3品의 堂上官 흉배.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>PS0100200100100420400000</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1486,8 +1774,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>29576</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>29576</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1512,19 +1802,31 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8407629.do</t>
+          <t>한국-일제강점</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8407629.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>가로 : 17.2 세로 : 18</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>조선시대 문관의 상복(常服)에 부착하여 품계(品階)를 나타내는 표시. 단학흉배는 문관 당하관이 착용한 흉배이며, 지방관원이나 육조(六曹) 가운데 품계가 낮은 관원들이 공복(公服)에 착용함. 검정색 명주 바탕에 가운데에는 불로초를 입에 물고 날개를 활짝 편 학과 오색구름을 비롯하여 물결·바위등의 십장생무늬가 견사로 수놓여 있음. 사각의 테두리는 황토색으로 수놓임. 일본어로 인쇄된 신문이 흉배 뒷부분에 대어져 있음. 29575와 한 조임.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
           <t>PS0100200100102957600000</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1542,8 +1844,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>628</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1568,19 +1872,31 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8288762.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8288762.do; https://www.nfm.go.kr/common/apiimage/relic/8288763.do</t>
+          <t>의-의류-부분품-보/흉배 / 주-생활용품/가전-장식용구</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>세로 : 59 가로 : 59</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>녹색 공단 바탕에 마주보는 봉황 사이에 如意珠를 두고, 구름·바위·물결·물방울·犀角·구름문 등은 주위에 배치한 봉황흉배. 봉황은 白色絲로 놓음. 테두리는 밤색. 王妃의 圓衫 흉배. 남상민 복원 제작품.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
           <t>PS0100200100900062800000</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1598,8 +1914,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>631</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1624,19 +1942,31 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8559501.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8559501.do; https://www.nfm.go.kr/common/apiimage/relic/8559504.do; https://www.nfm.go.kr/common/apiimage/relic/8559503.do; https://www.nfm.go.kr/common/apiimage/relic/8559502.do</t>
+          <t>의-의류-부분품-보/흉배 / 주-생활용품/가전-장식용구</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>세로 : 59 가로 : 59</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>청녹색 공단 바탕에 머리를 뒤로 돌린 거북을 두고 주변에는 구름을 비롯하여 물결·바위·물방울·산호·불로초 등을 金絲로 표현한 거북 흉배 1쌍. 거북의 입에서 나오는 불길은 홍색으로 강조함. 大君用. 남상민 복원 제작품.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
           <t>PS0100200100900063100000</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1654,8 +1984,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>77384</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>77384</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1676,19 +2008,31 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8412016.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8412016.do</t>
+          <t>의-의류-의례복 / 사회생활-의례생활-상장</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
+          <t>길이 : 430 너비 : 104</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>여성용 하의(下衣). 무연고 여자 묘(경기도 남양주 별내면 화접리 4-1지점 묘6)에서 출토된 대렴의(大斂衣). 7.5폭 겹옷. 운문단(雲紋緞)으로 만들어짐. 직사각 형태. 무릎에 해당하는 두 부분에 사자흉배(세로 33 가로 37.5)가 부착됨. 흉배는 연금사로 짜여 지고, 무늬가 반쪽만 직성(織成)된 2폭이 이어져 만들어짐. 말기와 허리끈 없음.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
           <t>PS0100200100107738400000</t>
         </is>
       </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1706,8 +2050,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>29575</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>29575</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1732,19 +2078,31 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8335546.do</t>
+          <t>한국-일제강점</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8335546.do</t>
+          <t>의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>세로 : 18 가로 : 17</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>조선시대 문관의 상복(常服)에 부착하여 품계(品階)를 나타내는 표시. 단학흉배는 문관 당하관(堂下官)이 착용한 흉배이며, 지방관원이나 육조(六曹)가운데 품계가 낮은 관원들이 공복(公服)에 착용함. 검정색 명주 바탕에 불로초를 입에 물고 날개를 활짝 편 형태의 단학흉배임. 오색구름을 비롯하여 물결·바위는 견사로 수놓여 있으며, 사각의 테두리는 황토색으로 수놓임. 영문이 인쇄된 종이가 뒤에 대어져 있음. 29576과 한 조임.</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
           <t>PS0100200100102957500000</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1762,8 +2120,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>28063</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>28063</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1788,19 +2148,31 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8333540.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8333540.do</t>
+          <t>의-의류-의례복-남자수의</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
+          <t>화장 : 121 길이 : 126 품 : 54</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>둥근 깃의 남성용 겉옷. 충남 태안군 태안읍 삭선리 남오성(1643~1712년) 묘 출토. 단령은 항라(亢羅), 직령은 운문사(雲文紗)임. 단령과 직령이 붙어있는 형태. 각각 따로 제작된 단령과 직령을 깃, 수구, 밑단, 양쪽 무 부분만 실로 고정시켰음. 겉고름 3개와 안고름 2개가 모두 있음. 단령의 깃부분에 매듭단추와 고리가 있음. 뒤쪽 겨드랑이 양쪽에 고리가 달려 있음.</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>PS0100200100102806300000</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1818,8 +2190,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>28064</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>28064</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1844,19 +2218,31 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8517967.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8517967.do</t>
+          <t>의-의류-의례복-남자수의</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
+          <t>화장 : 120.5 길이 : 125 품 : 57</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>둥근 깃의 남성용 겉옷. 충남 태안군 태안읍 삭선리 남오성(1643~1712) 묘 출토. 단령(겉)과 직령(안)이 붙어 있는 형태. 단령은 운보문단(雲寶文緞)이고, 직령은 세주(細紬)임. 소매는 두리소매이며 길의 양 옆에 무가 달려 있음. 뒷길 겨드랑이 양옆에 각대를 걸 수 있는 고리와 무를 고정하는 매듭고리가 각각 한 개씩 달려있음. 안고름 2개와 겉고름 3개(단령고름 2개, 직령고름 1개)가 그대로 남아 있음.</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
           <t>PS0100200100102806400000</t>
         </is>
       </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1874,8 +2260,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>45555</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>45555</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1900,19 +2288,31 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8395306.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8395306.do; https://www.nfm.go.kr/common/apiimage/relic/8395307.do; https://www.nfm.go.kr/common/apiimage/relic/8395308.do; https://www.nfm.go.kr/common/apiimage/relic/8395309.do</t>
+          <t>의-의류-평상복-남자포류 / 사회생활-의례생활-상장</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
+          <t>길이 : 131.5 품 : 55 화장 : 125.5</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>남성용 포(袍). 이진숭(李鎭嵩, 1702~1756) 묘에서 출토된 보공품(補空品). 겹옷. 둥근 깃의 단령(團領) 안에 받침으로 직령(直領)이 수구, 섶, 무, 도련에 고정되고, 단령과 직령의 솔기가 서로 마주보는 형태. 운보문단(雲寶紋緞)으로 만들어짐. 두리소매에, 앞뒤 무 상단이 삼각형으로 접혀짐. 어깨와 겨드랑이 부분에 바대가 덧대짐. 단령 깃 끝부분 바느질이 뜯어지고, 겉깃 끝부분 여밈단추 없음. 동정과 고름 없음. 대(帶)를 끼우는 고리 없음. 쪽색 일부 남아 있음.</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>PS0100200100104555500000</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1930,8 +2330,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>77593</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>77593</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1956,19 +2358,31 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8411003.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8411003.do</t>
+          <t>사회생활-의례생활-상장 / 의-의류-의례복-남자수의</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
+          <t>화장 : 118 길이 : 136 품 : 50</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>남성용 포(袍). 신광헌(申光憲, 1731~1784) 묘(경기도 남양주 별내면 화접리 6-6지점 묘77)에서 출토된 대렴의(大斂衣). 겹옷. 주(紬)로 만들어짐. 둥근깃의 단령(團領) 안에 받침으로 직령(直領)이 수구, 섶, 도련에 고정되고, 단령과 직령의 솔기가 서로 마주보는 형태. 두리소매로 무 상단이 삼각형으로 접히고, 길 쪽으로 고정되었던 흔적 있음. 동정과 고름 없음.</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
           <t>PS0100200100107759300000</t>
         </is>
       </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1986,8 +2400,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>45553</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>45553</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2012,19 +2428,31 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8381309.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8381309.do; https://www.nfm.go.kr/common/apiimage/relic/8381312.do</t>
+          <t>사회생활-의례생활-상장 / 의-의류-평상복-남자포류</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t>길이 : 129 화장 : 125 품 : 52.5</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>남성용 포(袍). 이진숭(李鎭嵩, 1702~1756) 묘에서 출토된 보공품(補空品). 겹옷. 둥근 깃의 단령(團領) 안에 받침으로 직령(直領)이 수구, 섶, 무, 도련에 고정된 형태. 운보문사(雲寶紋紗)로 만들어짐. 두리소매에, 앞뒤 무 상단이 삼각형으로 접혀짐. 단령과 직령의 어깨와 겨드랑이 부분에 바대가 덧대짐. 동정과 고름 없고, 겉깃 끝부분에 여밈 단추 없음. 대(帶)를 끼우는 고리 없음.</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
           <t>PS0100200100104555300000</t>
         </is>
       </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2042,8 +2470,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>45554</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>45554</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2068,19 +2498,31 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8561504.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8561504.do; https://www.nfm.go.kr/common/apiimage/relic/8561501.do; https://www.nfm.go.kr/common/apiimage/relic/8561502.do; https://www.nfm.go.kr/common/apiimage/relic/8561503.do</t>
+          <t>의-의류-평상복-남자포류 / 사회생활-의례생활-상장</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t>길이 : 129.5 품 : 57 화장 : 127.5</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>남성용 포(袍). 이진숭(李鎭嵩, 1702~1756) 묘에서 출토된 보공품(補空品). 겹옷. 둥근 깃의 단령(團領) 안에 받침으로 직령(直領)이 수구, 섶, 무, 도련에 고정된 형태. 주(紬)로 만들어짐. 두리소매에, 앞뒤 무 상단이 삼각형으로 접혀짐. 겉감 앞길 식서 부분에 '定織加長淸水重絹', 안감 앞길 식서 부분에는 '○○加長'이 묵서(墨書)됨. 깃 끝에 암단추와 고대점 부분에 숫단추가 달림. 단령 깃 끝부분 바느질이 뜯어지고, 고름은 끝부분 일부만 남음. 동정 없음.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
           <t>PS0100200100104555400000</t>
         </is>
       </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2098,8 +2540,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>28065</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>28065</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2124,19 +2568,31 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8333495.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8333495.do</t>
+          <t>의-의류-의례복-남자수의</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
+          <t>길이 : 132 화장 : 127 품 : 59</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>둥근 깃의 남성용 겉옷. 충남 태안군 태안읍 삭선리 남오성(1643~1712)묘 출토. 겉감과 안감은 운보문단(雲寶紋緞)임. 단령과 직령을 각각 제작한 후 안쪽 면을 마주대고 징궈서 고정한 형태임. 두리소매임. 겉고름 3개와 안고름 3개가 모두 있음. 뒷길 양 겨드랑이 쪽에는 각대를 거는 고리가 붙어 있음. 그 양 옆에는 각각 끈이 붙어 있음. 단령의 깃부분에는 매듭단추와 고리가 있음.</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
           <t>PS0100200100102806500000</t>
         </is>
       </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2154,8 +2610,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>9782</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>9782</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2176,19 +2634,31 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8271732.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8271732.do; https://www.nfm.go.kr/common/apiimage/relic/8271730.do; https://www.nfm.go.kr/common/apiimage/relic/8271731.do</t>
+          <t>의-의류-의례복-남자수의</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
+          <t>품 : 56 길이 : 125 화장 : 114</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>겉감은 짙은 밤색 갑사, 안감은 명주. 깃은 단령. 뒤로 돌려 붙은 무의. 중심에서 양옆의 무가 만나는 형태.</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
           <t>PS0100200100100978200000</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2206,8 +2676,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>1095</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1095</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2232,19 +2704,31 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8403056.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8403056.do</t>
+          <t>의-의류-평상복</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>화장 : 127.5 길이 : 138.5</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>남성용 포. 조선전기의 출토품 재현품. 분홍색 모시로 만든 여름용 홑옷. 깃은 단령이고 소매가 긴 형태. 사다리꼴형의 무가 트여 있음. 왼쪽 깃 끝에 매듭단추가 달림. 안고름과 여밈끈 2쌍이 있음. 손바느질.</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
           <t>PS0100200100900109500000</t>
         </is>
       </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2262,8 +2746,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>75111</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>75111</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2288,19 +2774,31 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8443996.do</t>
+          <t>한국-대한제국</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8443996.do</t>
+          <t>의-의류-백관복-상복</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
+          <t>등길이 : 124 품 : 50.5 화장 : 97.5</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>깃을 둥글게 만든 남성용 포(袍). 깃이 둥글고 소매가 넓으며, 옷자락이 무릎 아래까지 내려오는 형태. 명주(明紬)로 만들어진 겹옷임. 겉은 단령깃, 안은 직령깃으로 하여 붙임. 양쪽 허리 부분에 대고리와 끈 1쌍이 각각 달림. 겉고름 3개, 안고름 3개 달림. 앞뒷길에 흉배 부착됨.</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
           <t>PS0100200100107511100000</t>
         </is>
       </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2318,8 +2816,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>90548</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>90548</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2344,19 +2844,31 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8507198.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8507198.do; https://www.nfm.go.kr/common/apiimage/relic/8507199.do; https://www.nfm.go.kr/common/apiimage/relic/8507197.do</t>
+          <t>의-의류-의례복-남자제례복</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t>화장 : 82 길이 : 125 품 : 57</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>깃을 둥글게 만든 남성용 포(袍). 깃이 둥글고 소매가 넓으며, 옷자락이 무릎 아래까지 내려오는 형태. 문사(紋紗)로 만들어진 홑옷임. 단령깃 안쪽에 직령깃만 마름하여 부착됨. 직령깃 내부에 종이심 있음. 겉고름 1쌍, 안고름 1쌍 달림. 무는 접혀 뒷길에 고정됨. 기증자의 집안에서 제사지낼 때 착용하였던 의복임.</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>PS0100200100109054800000</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2374,8 +2886,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>325</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2400,19 +2914,31 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8529543.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8529543.do</t>
+          <t>의-의류-백관복</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
+          <t>화장 : 97 품 : 56 길이 : 123</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>남성용 포(袍). 백관이 입는 관복. 겉감은 검은색 갑사로 만들고 안감은 남색 항라로 만든 겹옷임. 소매가 넓고 깃이 둥근 형태임. 넓은 동정이 달리고 안고름과 겉고름이 있음. 겉고름 한쪽은 겹고름임. 겨드랑이에는 띠 고리와 끈이 달려 있음. 무는 뒤로 접어 징그고 하단은 트인 채로 둠. 각 단은 검은색의 선(襈)을 덧댐. 손바느질.</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
           <t>PS0100200100100032500000</t>
         </is>
       </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2430,8 +2956,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>974</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>974</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2456,19 +2984,31 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8494859.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8494859.do</t>
+          <t>의-의류-백관복</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t>길이 : 126.5 품 : 50 화장 : 89</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>남성용 포(袍). 백관이 입는 관복. 겉감은 검은색 운보문사(雲寶文紗)로 만들고 안감은 홍색 운보문사로 만든 겹옷임. 소매가 넓고 깃이 둥근 형태임. 넓은 동정이 달리고 안고름과 겉고름이 있음. 고름은 겹고름임. 겨드랑이에는 띠를 거는 끈 1쌍이 달려 있음. 무는 뒤로 접어 징그고 하단은 트인 채로 둠. 손바느질.</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
           <t>PS0100200100100097400000</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2486,8 +3026,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>1923</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2512,19 +3054,31 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8250621.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8250621.do</t>
+          <t>의-의류-백관복</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
+          <t>길이 : 116.5 품 : 47.5 화장 : 87.5</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>남성용 포(袍). 백관이 입던 관복. 겉감은 녹청색 운문사(雲文紗)로 만들고 안감은 남색 운문사로 만든 겹옷임. 소매가 넓고 깃이 둥근 형태임. 넓은 동정이 달리고 안고름과 겉고름이 있음. 겨드랑이에는 띠고리와 끈 1쌍이 달려 있음. 무는 뒤로 접어 징그고 하단은 트인 채로 둠. 가슴과 등에 쌍학흉배가 부착됨. 손바느질.</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
           <t>PS0100200100100192300000</t>
         </is>
       </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2542,8 +3096,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>2409</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2568,19 +3124,31 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8530693.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8530693.do</t>
+          <t>의-의류-백관복</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
+          <t>품 : 52 화장 : 92 길이 : 121.5</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>남성용 포(袍). 백관이 입던 관복. 겉감은 보라색 견직물이고 안감은 남색 견직물로 만든 겹옷임. 소매가 넓고 깃이 둥근 형태임. 넓은 동정이 달리고 안고름과 겉고름이 있음. 겉고름 한쪽은 겹고름임. 겨드랑이에는 띠를 거는 끈 1쌍이 달려 있음. 무는 뒤로 접어 징그고 하단은 트인 채로 둠. 가슴과 등에 단학흉배(單鶴胸背)가 부착됨. 손바느질.</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
           <t>PS0100200100100240900000</t>
         </is>
       </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2598,8 +3166,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>4896</v>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4896</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2624,19 +3194,31 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8243226.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8243226.do</t>
+          <t>의-의류-백관복</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
+          <t>길이 : 119.5 화장 : 87.5 품 : 45</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>남성용 포(袍). 백관이 입는 관복. 겉감은 운보문이 있는 군청색 숙고사로 만들고 안감은 분홍색 면직물로 만든 겹옷임. 소매가 넓고 깃이 둥근 형태임. 넓은 동정이 달리고 안고름과 겉고름이 있음. 겨드랑이에는 띠를 거는 끈 1쌍이 달려 있음. 무는 뒤로 접어 징그고 하단은 트인 채로 둠. 손바느질.</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
           <t>PS0100200100100489600000</t>
         </is>
       </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2654,8 +3236,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>4999</v>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4999</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2680,19 +3264,31 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8495893.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8495893.do</t>
+          <t>의-의류-백관복</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
+          <t>화장 : 94 길이 : 116 품 : 46</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>백관이 입는 관복. 겉감은 북청색 운문사(雲文絲)로 만들고 안감은 청색 운문사로 만든 겹옷임. 소매가 넓고 깃이 둥근 형태임. 안고름과 겉고름 한쌍이 달림. 고름 한짝은 겹고름임. 겨드랑이에는 띠를 거는 고리와 끈 1쌍이 달려 있음. 무는 뒤로 접어 징그고 하단은 트인 채로 둠. 손바느질.</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
           <t>PS0100200100100499900000</t>
         </is>
       </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2710,8 +3306,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>5082</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>5082</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2736,19 +3334,31 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8273339.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8273339.do</t>
+          <t>의-의류-백관복</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
+          <t>화장 : 79 품 : 49.5 길이 : 120</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>백관이 입던 관복. 겉감은 녹청색 운문사(雲文絲)로 만들고 안감은 파란색 운문사로 만든 겹옷임. 소매는 직배래이며 깃이 둥근 형태임. 넓은 동정이 달리고 안고름과 겉고름이 있음. 옆선에 손을 넣을 수 있도록 트임을 냄. 손바느질.</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
           <t>PS0100200100100508200000</t>
         </is>
       </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2766,8 +3376,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>5882</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>5882</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2792,19 +3404,31 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8311414.do</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8311414.do</t>
+          <t>의-의류-백관복</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
+          <t>길이 : 114 화장 : 70 품 : 54</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>남성용 포. 백관이 입는 관복. 겉감은 수박색 화문단이고 안감은 살구색 견직물로 만든 겹옷임. 소매가 넓고 깃이 둥근 형태임. 넓은 동정이 달리고 겹고름 한쌍이 있음. 겨드랑이에는 띠를 거는 끈이 달려 있음. 무는 뒤로 접어 징그고 하단은 트인 채로 둠. 손바느질.</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
           <t>PS0100200100100588200000</t>
         </is>
       </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2822,8 +3446,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>5907</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2848,19 +3474,31 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8248879.do</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8248879.do</t>
+          <t>의-의류-백관복</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
+          <t>화장 : 87.5 품 : 51.5 길이 : 123</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>남성용 포. 백관이 입는 관복. 겉감은 자주색 순인이고 안감은 청색 순인으로 만든 겹옷임. 소매가 넓고 깃이 둥근 형태임. 넓은 동정이 달리고 안고름과 겉고름이 있음. 겨드랑이에는 띠를 거는 끈 1쌍이 달려 있음. 무는 뒤로 접어 징그고 하단은 트인 채로 둠. 손바느질.</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
           <t>PS0100200100100590700000</t>
         </is>
       </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2878,8 +3516,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>6352</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>6352</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2904,19 +3544,31 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8510276.do</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8510276.do</t>
+          <t>의-의류-의례복-남자혼례복</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
+          <t>품 : 47.5 화장 : 86 길이 : 121</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>남성용 혼례복. 겉감은 군청색 갑사로 만들고 안감은 남색 갑사로 만든 겹옷임. 소매가 넓고 깃이 둥근 형태임. 넓은 동정이 달리고 안고름과 겉고름이 있음. 겨드랑이에는 띠 고리와 끈이 달려 있음. 무는 뒤로 접어 징그고 하단은 트인 채로 둠. 손바느질.</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
           <t>PS0100200100100635200000</t>
         </is>
       </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2934,8 +3586,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>6353</v>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6353</t>
+        </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2960,19 +3614,31 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8249401.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8249401.do</t>
+          <t>의-의류-백관복</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
+          <t>품 : 59 길이 : 114 화장 : 99</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>남성용 포(袍). 백관이 입는 관복. 겉감은 남색 양단이고 안감은 녹색 합성섬유로 만든 겹옷임. 소매가 넓고 깃이 둥근 형태임. 안고름과 겉고름 한쌍이 있음. 겨드랑이에는 띠를 거는 끈이 달려 있음. 무는 뒤로 접어 징그고 하단은 트인 채로 둠. 재봉틀 바느질.</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
           <t>PS0100200100100635300000</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2990,8 +3656,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>7269</v>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>7269</t>
+        </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -3016,19 +3684,31 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8312161.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8312161.do</t>
+          <t>의-의류-백관복-공복</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
+          <t>길이 : 118 품 : 52.5 화장 : 97</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>남성용 포(袍). 백관이 입던 관복. 겉감은 녹청색 견직물로 만들고 안감은 남색 견직물로 만든 겹옷임. 소매가 넓고 깃이 둥근 형태임. 넓은 동정이 달리고 안고름과 겉고름이 있음. 겨드랑이에는 띠 고리와 끈이 달려 있음. 띠고리에는 술이 일부 달려 있음. 무는 뒤로 접어 징그고 하단은 트인 채로 둠. 가슴과 등에 흉배를 달았던 흔적 있음. 손바느질.</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
           <t>PS0100200100100726900000</t>
         </is>
       </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3046,8 +3726,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D48" t="n">
-        <v>9532</v>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>9532</t>
+        </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -3072,19 +3754,31 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8535034.do</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8535034.do</t>
+          <t>의-의류-궁중복-공복</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
+          <t>길이 : 120 품 : 55 화장 : 82</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>남성용 포. 백관이 입는 관복. 겉감은 녹색 갑사이고 안감은 남색 갑사로 만든 겹옷임. 소매가 넓고 깃이 둥근 형태임. 넓은 동정이 달리고 겉고름과 안고름이 있음. 무는 뒤로 접어 뒷길 안쪽 부분에 징그고 하단은 트인 채로 둠.</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
           <t>PS0100200100100953200000</t>
         </is>
       </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3102,8 +3796,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>9649</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>9649</t>
+        </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -3124,19 +3820,31 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8297873.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8297873.do; https://www.nfm.go.kr/common/apiimage/relic/8297874.do; https://www.nfm.go.kr/common/apiimage/relic/8297872.do</t>
+          <t>의-의류-의례복-남자수의</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
+          <t>길이 : 117.5 품 : 66 화장 : 130</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>무명. 홑. 깃은 단련. 배래를 약간 굴림. 끈 2개(명주 3 x 26) 직사각형의 무가 달려있음.(주름이 펴진 상태) 무명 한폭 37cm.</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
           <t>PS0100200100100964900000</t>
         </is>
       </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3154,8 +3862,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>20960</v>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>20960</t>
+        </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -3176,19 +3886,31 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8395624.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8395624.do; https://www.nfm.go.kr/common/apiimage/relic/8395625.do</t>
+          <t>의-의류-의례복-남자수의</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
+          <t>품 : 63 길이 : 149 화장 : 122</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>목선이 둥근 남성용 겉옷. 홑옷. 옷감은 명주임. 겉섶 끝, 겨드랑이, 안깃 끝, 옆선에 고리가 있음. 어깨와 겨드랑이에 바대를 댐. 1폭은 약 34cm임. 깃 끝에 매듭단추가 달렸던 흔적이 있음. 변수(邊脩, 1447-1524) 묘에서 출토된 자료임.</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
           <t>PS0100200100102096000000</t>
         </is>
       </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3206,8 +3928,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>20961</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>20961</t>
+        </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -3228,19 +3952,31 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8283074.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8283074.do; https://www.nfm.go.kr/common/apiimage/relic/8283075.do</t>
+          <t>의-의류-의례복-남자수의</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
+          <t>길이 : 140.5 품 : 68 화장 : 122.5</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>목선이 둥근 남성용 겉옷. 홑옷. 옷감은 사(紗)이고, 운보문(雲寶紋)이 있음. 어깨와 겨드랑이에 바대를 댐. 1폭은 약 66cm임. 겉섶 끝, 겨드랑이, 안깃 끝, 옆선에 고리 흔적 있음. 깃 끝에 매듭단추가 달렸던 흔적이 있음. 변수(邊脩, 1447-1524) 묘에서 출토된 자료임.</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
           <t>PS0100200100102096100000</t>
         </is>
       </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3258,8 +3994,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D52" t="n">
-        <v>24381</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>24381</t>
+        </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -3280,19 +4018,31 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8312910.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8312910.do</t>
+          <t>의-의류-의례복-남자수의</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
+          <t>품 : 60 길이 : 128 화장 : 113</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>목선이 둥근 남성용 겉옷. 충북 옥천군 옥천읍 대천리 출토. 홑. 황갈색 면주(綿紬)임. 수구가 좁아지는 통수(筒袖) 형식. 깃은 사선으로 재단되고, 여밈부분에 매듭단추 1쌍이 달림. 뒷길 겨드랑이 아래에 각대를 거는 고리가 달려 있음. 어깨에 U자형 등바대·좌우 진동에 소요형 옆바대가 달림. 길이 3조각으로 나뉘어져 있음.</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
           <t>PS0100200100102438100000</t>
         </is>
       </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3310,8 +4060,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>28017</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>28017</t>
+        </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -3336,19 +4088,31 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8333267.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8333267.do; https://www.nfm.go.kr/common/apiimage/relic/8333268.do</t>
+          <t>의-의류-의례복-남자수의</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
+          <t>화장 : 102 품 : 72 길이 : 120</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>둥근 깃의 남성용 겉옷. 충북 보은군 마로면 적암리 류인서(?~1644) 부부 묘 출토. 홑옷. 안깃 끝에 안고름이 하나 달려있음. 겉고름은 없음. 한폭은 약 35cm. 겉깃 끝과 겨드랑이에 매듭단추가 달려있음. 등과 겨드랑이에 바대가 있음.</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
           <t>PS0100200100102801700000</t>
         </is>
       </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3366,8 +4130,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D54" t="n">
-        <v>28023</v>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>28023</t>
+        </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3392,19 +4158,31 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8333365.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8333365.do</t>
+          <t>의-의류-의례복-남자수의</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
+          <t>화장 : 128.5 길이 : 124 품 : 74</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>둥근 깃의 남성용 겉옷. 충북 보은군 마로면 적암리 류인서(?~1644) 부부 묘 출토. 홑옷. 한폭 34.5cm. 수구가 좁아지는 통수(筒袖) 형식으로 배래가 둥근 모양임. 길 양옆 트임이 있음. 직사각형 무의 겨드랑이쪽에는 고리로 연결되어 있어, 무가 하단으로 처지지 않게 잡아주는 역할을 함. 등의 상단부 안쪽에 바대를 덧대었으며, 겨드랑이의 고리 부분에는 네모난 바대를 덧댐. 깃의 매듭단추는 결손되고 흔적만 남아 있으며 고리는 그대로 남아있음.</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
           <t>PS0100200100102802300000</t>
         </is>
       </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3422,8 +4200,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D55" t="n">
-        <v>31861</v>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>31861</t>
+        </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -3448,19 +4228,31 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8347752.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8347752.do; https://www.nfm.go.kr/common/apiimage/relic/8347753.do</t>
+          <t>의-의류-백관복-공복</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
+          <t>등길이 : 123.5 품 : 57 화장 : 92</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>조선시대 백관(百官)이 입던 깃을 둥글게 만든 관복(官服). 겉감은 보라색 견사(絹紗)로 만들고, 안감은 청남색 견사로 만든 겹옷임. 소매(통 44)가 넓고, 깃(너비 4.7~5, 길이 25.5)이 둥근 형태임. 넓은 동정이 달리고, 안고름(너비 10, 길이 76)과 겉고름(너비 10, 길이 96)이 있음. 겨드랑이에는 띠고리와 끈 한 쌍이 달려 있음. 무는 뒤로 접어 징그고, 하단은 트인 채로 둠. 가슴과 등에는 금사(金絲)로 엮은 쌍학흉배(세로 18, 가로 20)가 부착됨. 손바느질됨.</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
           <t>PS0100200100103186100000</t>
         </is>
       </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3478,8 +4270,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>34543</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>34543</t>
+        </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3504,19 +4298,31 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8347561.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8347561.do</t>
+          <t>의-의류-의례복-남자관례복</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
+          <t>화장 : 77.5 길이 : 126</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>남성용 혼례복. 겉감은 군청색 갑사로 만들고 안감은 파란색 갑사로 만든 겹옷. 소매통은 좁고, 직배래임. 안고름과 겉고름이 한 쌍 씩 달려 있음. 겨드랑이에는 띠를 거는 고리가 있음. 흉배를 달았던 흔적이 있음.</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
           <t>PS0100200100103454300000</t>
         </is>
       </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3534,8 +4340,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D57" t="n">
-        <v>34555</v>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>34555</t>
+        </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -3560,19 +4368,31 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8354978.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8354978.do</t>
+          <t>의-의류-백관복</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
+          <t>품 : 50 화장 : 92 길이 : 124</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>백관이 입던 관복으로 문무백관은 예복으로도 착용함. 겉감은 암청색 견이고, 안감은 청색 인조견으로 만든 겹옷. 소매가 넓고 깃이 둥근 형태임. 동정, 안고름과 겉고름이 달림. 겨드랑이에는 끈이 달려 있음. 흉배를 달았던 흔적이 있음.</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
           <t>PS0100200100103455500000</t>
         </is>
       </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3590,8 +4410,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D58" t="n">
-        <v>34556</v>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>34556</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3616,19 +4438,31 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8560146.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8560146.do</t>
+          <t>의-의류-백관복</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
+          <t>길이 : 120 품 : 48 화장 : 69</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>백관이 입던 관복으로 문무백관은 예복으로도 착용함. 겉감은 청색 갑사이고 안감은 운용문이 장식된 주홍색 갑사로 만든 겹옷. 소매가 넓고 깃이 둥근 형태임. 동정과 고름이 달림. 겨드랑이에는 끈이 달려 있음. 양 옆에 트임이 있음.</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
           <t>PS0100200100103455600000</t>
         </is>
       </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3646,8 +4480,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D59" t="n">
-        <v>34557</v>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>34557</t>
+        </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3672,19 +4508,31 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8347566.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8347566.do</t>
+          <t>의-의류-백관복</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
+          <t>길이 : 126 화장 : 85</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>백관이 입던 관복으로 문무백관은 예복으로도 착용함. 겉감은 흑색 갑사이고 안감은 청색 갑사임. 소매가 넓고 깃이 둥근 형태임. 동정과 고름이 달림. 겨드랑이에는 끈과 고리가 달림.</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
           <t>PS0100200100103455700000</t>
         </is>
       </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3702,8 +4550,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D60" t="n">
-        <v>42321</v>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>42321</t>
+        </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3728,19 +4578,31 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8548072.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8548072.do</t>
+          <t>의-의류-의례복-남자혼례복</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
+          <t>품 : 57 등길이 : 121 화장 : 77</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>관원의 집무복. 남성 혼례복으로 사용됨. 둥근 깃 안에 직령(直領)깃이 달린 형태. 겉섶에는 고름 1쌍, 양쪽 겨드랑이에는 대(帶)를 끼우는 고리가 달림. 앞길의 사다리꼴 무는 뒤로 접혀져 고정됨. 무의 상단에서 아래로 38.5cm까지 바느질되어 있고, 이하는 트여 있음. 가슴에 쌍학(雙鶴)이 수(繡) 놓여진 정사각형의 흉배가 부착됨. 42321-42324 한 조임.</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
           <t>PS0100200100104232100000</t>
         </is>
       </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3758,8 +4620,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D61" t="n">
-        <v>66029</v>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>66029</t>
+        </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -3784,19 +4648,31 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8427646.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8427646.do; https://www.nfm.go.kr/common/apiimage/relic/8427647.do; https://www.nfm.go.kr/common/apiimage/relic/8427645.do</t>
+          <t>의-의류-의례복-남자혼례복</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
+          <t>품 : 57 등길이 : 123 화장 : 81</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>깃을 둥글게 만든 남성용 포(袍). 혼례복(婚禮服). 깃이 둥글고 소매가 넓으며, 옷자락이 무릎 아래까지 내려오는 형태. 겉감은 '喜'자와 백조 무늬가 짜여진 청색 사(紗), 안감은 같은 무늬의 홍색 사(紗)로 만든 겹옷임. 둥근 깃 안에 칼깃이 덧붙여짐. 깃 여밈 부분에는 매듭단추와 고리 부착됨. 앞길에 겉고름 1쌍, 양쪽 겨드랑이에 대(帶)를 걸기 위한 끈 1쌍이 각각 달림. 무는 뒤로 접어 박고, 옆선 하단은 트여 있음(길이 39). 깃 내면에 종이 심지 있음. 재봉틀 바느질.</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
           <t>PS0100200100106602900000</t>
         </is>
       </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3814,8 +4690,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D62" t="n">
-        <v>67186</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>67186</t>
+        </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -3840,19 +4718,31 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8430573.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8430573.do; https://www.nfm.go.kr/common/apiimage/relic/8430574.do; https://www.nfm.go.kr/common/apiimage/relic/8430572.do</t>
+          <t>의-의류-백관복</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
+          <t>화장 : 72 품 : 61 등길이 : 115</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>깃을 둥글게 만든 포(袍). 남성 혼례복(婚禮服). 겉감은 '喜'자와 쌍봉 무늬가 짜여진 청색 사(紗), 안감은 무늬가 없는 홍색 사(紗)로 만든 겹옷임. 가슴과 등에 쌍학흉배 1쌍 부착됨.</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
           <t>PS0100200100106718600000</t>
         </is>
       </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3870,8 +4760,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D63" t="n">
-        <v>67467</v>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>67467</t>
+        </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -3896,19 +4788,31 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8430046.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8430046.do</t>
+          <t>의-의류-종교복-무복</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
+          <t>화장 : 82 등길이 : 125 품 : 64</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>무당이 굿 할 때 입던 무복(巫服). 깃을 둥글게 만든 포(袍). 남성용. 문양이 짜여진 사(紗)직물로 만들어진 홑겹 옷임. 재봉틀 바느질.</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
           <t>PS0100200100106746700000</t>
         </is>
       </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3926,8 +4830,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D64" t="n">
-        <v>70801</v>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>70801</t>
+        </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3952,19 +4858,31 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8445951.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8445951.do</t>
+          <t>의-의류-백관복-상복</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
+          <t>화장 : 92.5 길이 : 130 품 : 49.5</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>깃을 둥글게 만든 포(袍). 깃이 동글고 소매가 넓으며 옷자락이 긴 형태. 겉감은 운문사(雲紋紗), 안감도 같은 무늬의 사(紗)로 만든 겹옷. 둥근 깃 안에 동정이 달림. 깃 여밈 부분에는 매듭단추와 고리 부착됨. 겉고름과 안고름 1쌍이 각각 달림. 겨드랑이 양쪽에 띠고름 1쌍이 달려 있음. 가슴과 등에 쌍호흉배(雙虎胸背)가 부착됨. 옆선 하단 트임 있음.</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
           <t>PS0100200100107080100000</t>
         </is>
       </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3982,8 +4900,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D65" t="n">
-        <v>70817</v>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>70817</t>
+        </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -4008,19 +4928,31 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8446720.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8446720.do</t>
+          <t>의-의류-백관복-상복</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
+          <t>품 : 49 화장 : 93.5 길이 : 122</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>깃을 둥글게 만든 포(袍). 깃이 동글고 소매가 넓으며 옷자락이 긴 형태. 겉감은 운문사(雲紋紗), 안감도 같은 무늬의 사(紗)로 만든 겹옷. 둥근 깃 안에 동정이 달림. 깃 여밈 부분에는 매듭단추와 고리 부착됨. 겉고름과 안고름 1쌍이 각각 달림. 오른쪽 겨드랑이 아래 띠고름 1개 남아 있음. 가슴과 등에 단호흉배(單虎胸背)가 부착됨. 옆선 하단 트임 있음.</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
           <t>PS0100200100107081700000</t>
         </is>
       </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4038,8 +4970,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D66" t="n">
-        <v>72260</v>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>72260</t>
+        </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -4064,19 +4998,31 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8440142.do</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8440142.do</t>
+          <t>의-의류-백관복-상복</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
+          <t>등길이 : 126 품 : 50 화장 : 102.5</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>깃을 둥글게 만든 포(袍). 명주에 쪽물을 들여 만든 겹옷임.</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
           <t>PS0100200100107226000000</t>
         </is>
       </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4094,8 +5040,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D67" t="n">
-        <v>77457</v>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>77457</t>
+        </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -4120,19 +5068,31 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8385172.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8385172.do</t>
+          <t>사회생활-의례생활-상장 / 의-의류-의례복</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
+          <t>품 : 68 화장 : 90 길이 : 133.5</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>여성용 포(袍). 고령신씨 여자 묘(경기도 남양주 별내면 화접리 4-5지점 묘13)에서 출토된 소렴의(小斂衣). 홑옷. 운문사(雲紋紗)로 만들어짐. 둥근깃에 통수(筒袖)형으로 배래가 직선인 형태. 무 상단에 맞주름이 잡히고, 각각 앞뒤 길 쪽으로 고정됨. 소매 부분 시접이 밖으로 연결됨. 여밈단추, 동정, 고름 없음. 쪽빛 일부 남아 있음.</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
           <t>PS0100200100107745700000</t>
         </is>
       </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4150,8 +5110,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D68" t="n">
-        <v>77534</v>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>77534</t>
+        </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -4176,19 +5138,31 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8572397.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8572397.do</t>
+          <t>의-의류-의례복-남자수의 / 사회생활-의례생활-상장</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
+          <t>화장 : 115 길이 : 124 품 : 71</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>남성용 포(袍). 무연고 남자 묘(경기도 남양주 별내면 화접리 6-2지점 묘4)에서 출토된 수의(壽衣). 홑옷. 초(綃)로 만들어짐. 둥근깃에 진동보다 수구 쪽이 넓어 배래가 곡선인 형태. 무 상단이 삼각형으로 접히고, 옆으로 펼쳐짐. 등, 어깨, 겨드랑이 부분에 바대가 덧대짐. 무와 섶선, 도련, 수구 안쪽에 선이 둘려짐. 앞이 짧고 뒤가 긴 전단후장(前短後長)임. 고대점 부분에는 암단추가, 겉깃 끝 부분에는 여밈단추가 달림.</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
           <t>PS0100200100107753400000</t>
         </is>
       </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4206,8 +5180,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D69" t="n">
-        <v>94865</v>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>94865</t>
+        </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -4232,19 +5208,31 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8484672.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8484672.do; https://www.nfm.go.kr/common/apiimage/relic/8484673.do; https://www.nfm.go.kr/common/apiimage/relic/8484671.do</t>
+          <t>의-의류-의례복-남자혼례복</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
+          <t>화장 : 75 길이 : 127.5 품 : 58</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>깃을 둥글게 만든 남성용 포(袍). 한국전쟁 이후 민간에서 착용한 혼례용 의복으로, 독일 상트오틸리엔수도원에서 경북 칠곡 왜관수도원으로 파견된 보나벤투라 슈스터 수사가 수집함. 겉감에 화문(花紋)·복자문(福字紋)이, 안감에 화문(花紋)·쌍희문(雙喜紋) 등이 직조된 겹옷. 넓은 소매에 옷자락이 긴 형태. 겉고름, 안고름이 달림. 깃 여밈 부분에 매듭단추와 고리가 부착됨. 뒷길과 옆선이 트여 있음. 가슴과 등 부분에 쌍학(雙鶴)이 수(繡) 놓인 흉배가 부착됨.</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
           <t>PS0100200100109486500000</t>
         </is>
       </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4262,8 +5250,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D70" t="n">
-        <v>514</v>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -4284,19 +5274,31 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8293640.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8293640.do</t>
+          <t>의-의류-궁중복</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
+          <t>길이 : 130 화장 : 89 진동 : 32</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>보유자. 자주색 겉감에 청색 안감. 쌍학 흉배 앞뒤로 달림.</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
           <t>PS0100200100700051400000</t>
         </is>
       </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4314,8 +5316,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D71" t="n">
-        <v>772</v>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -4336,19 +5340,31 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8301643.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8301643.do</t>
+          <t>의-의류-의례복-남자혼례복</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
+          <t>길이 : 128 화장 : 87.5 품 : 62</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>남성용 혼례복. 깃모양이 둥근 조선시대 상복(常服) 모양임. 겉감은 자주색 숙고사, 안감은 빨간색 숙고사로 만듦. 긴고름은 이중고름으로 되어 있으며 가슴과 등에 쌍학흉배가 달려 있음. 참772-참775 한조.</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
           <t>PS0100200100900077200000</t>
         </is>
       </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4366,8 +5382,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D72" t="n">
-        <v>1183</v>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1183</t>
+        </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -4392,19 +5410,31 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8309922.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8309922.do</t>
+          <t>의-의류-궁중복</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
+          <t>품 : 56 화장 : 89.5 길이 : 124.2</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>남성용 포. 창령위 김병주(1824~1888) 유품 복원품. 남자관복. 깃이 둥글고 소매가 넓은 형태. 겉감은 검자주색 순인, 안감은 감홍색의 갑사임. 뒤로 돌려붙은 무가 있음. 가슴과 등에는 쌍학문의 금사흉배가 있음. 동정이 달림. 안고름과 겉고름이 있고, 겉의 긴고름은 이중고름임. 어깨와 겨드랑이에 바대를 댐. 겨드랑이에 대대걸이와 끈이 달림. 손바느질.</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
           <t>PS0100200100900118300000</t>
         </is>
       </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4422,8 +5452,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>1186</v>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1186</t>
+        </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -4448,19 +5480,31 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8309243.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8309243.do</t>
+          <t>의-의류-의례복-남자혼례복</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
+          <t>길이 : 138.2 화장 : 92.5 품 : 61</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>남성용 포. 혼례용 예복. 겹옷. 소매가 넓고 깃이 둥근 형태. 겉감은 청현색 숙고사이며, 안감은 벽돌색 갑사임. 뒤로 돌려붙은 무가 있음. 동정이 달림. 안고름과 겉고름이 있고, 겉의 긴고름은 이중고름임. 대대걸이용 끈이 달려있음. 소매끝에 개밑단추가 있음. 가슴과 등에 쌍학문의 흉배가 있음. 손바느질.</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
           <t>PS0100200100900118600000</t>
         </is>
       </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4478,8 +5522,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D74" t="n">
-        <v>23879</v>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>23879</t>
+        </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -4504,19 +5550,31 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8525811.do</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8525811.do</t>
+          <t>의-의류-의례복</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
+          <t>화장 : 88.5 길이 : 100.5 품 : 54</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>관복 중의 하나. 나주향교에서 사용됨. 손바느질. 홑옷. 길 · 소매 · 고름은 검은색이고, 깃은 흰색임. 왼쪽 앞길에 붉은색 폐슬(蔽膝)이 달림. 단령 깃 안에 직령 깃이 달려 있음.</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
           <t>PS0100200100102387900000</t>
         </is>
       </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4534,8 +5592,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D75" t="n">
-        <v>23880</v>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>23880</t>
+        </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -4560,19 +5620,31 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8314559.do</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8314559.do; https://www.nfm.go.kr/common/apiimage/relic/8314560.do</t>
+          <t>의-의류-궁중복</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
+          <t>품 : 57.5 화장 : 94.5 길이 : 98</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>관복 중의 하나. 나주향교에서 사용됨. 손바느질. 홑옷. 길 · 소매 · 고름은 검은색이고, 깃은 흰색임. 왼쪽 앞길에 붉은색 폐슬(蔽膝)이 달림. 단령 깃 안에 직령 깃이 달려 있음. 양쪽 겨드랑이의 끈에 별도의 흰색 끈이 묶여 있음.</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
           <t>PS0100200100102388000000</t>
         </is>
       </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4590,8 +5662,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D76" t="n">
-        <v>81400</v>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>81400</t>
+        </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -4612,19 +5686,31 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8577334.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8577334.do; https://www.nfm.go.kr/common/apiimage/relic/8577335.do; https://www.nfm.go.kr/common/apiimage/relic/8577336.do; https://www.nfm.go.kr/common/apiimage/relic/8577337.do; https://www.nfm.go.kr/common/apiimage/relic/8577340.do; https://www.nfm.go.kr/common/apiimage/relic/8577339.do; https://www.nfm.go.kr/common/apiimage/relic/8577341.do; https://www.nfm.go.kr/common/apiimage/relic/8577332.do; https://www.nfm.go.kr/common/apiimage/relic/8577333.do; https://www.nfm.go.kr/common/apiimage/relic/8577338.do</t>
+          <t>문화예술-서화-회화-기타</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
+          <t>가로 : 37.5 세로 : 50.8</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>이선부(李善溥, 1646~1721)의 초상화첩. 1719년(숙종 46) 숙종의 기로연에 참석한 신하들에게 내린 화첩의 일부로 추정. 초상화첩과 보관상자로 구성됨. 초상화첩은 지본채색(紙本彩色). 표지 2장. 내지 3장. 이선부의 초상 1점과 숙종의 어제에 화답한 글 기재됨. 초상화에는 관복을 입은 상반신을 그림. 그림 위에 전서(篆書)로 '前副司直六松李公七十四歲眞' 기재. 표지 비단으로 감쌈. 표제 없음. 화첩 보관용 상자는 직육면체로 좌우로 펼칠 수 있도록 가운데 경첩이 있음.</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
           <t>PS0100200100108140000000</t>
         </is>
       </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4642,8 +5728,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D77" t="n">
-        <v>95558</v>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>95558</t>
+        </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -4668,19 +5756,31 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8581572.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8581572.do; https://www.nfm.go.kr/common/apiimage/relic/8581562.do; https://www.nfm.go.kr/common/apiimage/relic/8581569.do; https://www.nfm.go.kr/common/apiimage/relic/8581564.do; https://www.nfm.go.kr/common/apiimage/relic/8581570.do; https://www.nfm.go.kr/common/apiimage/relic/8581567.do; https://www.nfm.go.kr/common/apiimage/relic/8581568.do; https://www.nfm.go.kr/common/apiimage/relic/8581571.do; https://www.nfm.go.kr/common/apiimage/relic/8581563.do; https://www.nfm.go.kr/common/apiimage/relic/8581573.do; https://www.nfm.go.kr/common/apiimage/relic/8581565.do; https://www.nfm.go.kr/common/apiimage/relic/8581566.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
+          <t>가로 : 89.5 세로 : 151.5</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>조선 후기의 문신 정재기(鄭在箕, 1811~1879)을 그린 그림. 1869년 5월 제작. 초상, 보관천, 보관함, 자물쇠로 구성됨. 초상은 족자 형태. 견본채색(絹本彩色). 화폭 세로 151.8, 가로 88.5. 정재기가 사모를 쓰고 단학흉배의 관복을 입은 채 호피를 덮은 교의 위에 앉은 모습임. 뒷면 우측 하단에 '同治八年己巳五月十五日始二十五日畢畵師印在模謹倣'이 묵서됨. 별지에 '貌雖露矣心則難眞心與貌肖庶幾近人 介隱自贊', '海月圓面林虎蹲身移來三幅彷彿其人 栢庵贊', '謨旣凝重心亦溫仁心雖莫盡貌以之因 松圃謹識'이 묵서됨. 보관천은 직사각 천 3개의 상하단을 연결한 형태. 3개의 모서리에 끈이 달려있음. 보관함는 직육면 형태. 앞면에 자물쇠용 앞바탕이 부착됨. 앞바탕 외면에 기하문(幾何文) 등이 음각 장식됨. 뒷면 뚜껑과 몸체 연결부위에 제비추리 경첩 3개가 연결됨. 가장자리 중앙에 허릿대감잡이가 부착됨. 자물쇠는 'ㄷ'자형태. 아래쪽은 원통형으로 되어 있음. 측면에는 열쇠구멍이 일자로 나있음. 앞면에 기하문(幾何文) 등이 음각 장식됨.</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
           <t>PS0100200100109555800000</t>
         </is>
       </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4698,8 +5798,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D78" t="n">
-        <v>40455</v>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>40455</t>
+        </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -4720,19 +5822,31 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8551076.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8551076.do; https://www.nfm.go.kr/common/apiimage/relic/8551075.do; https://www.nfm.go.kr/common/apiimage/relic/8551074.do; https://www.nfm.go.kr/common/apiimage/relic/8551073.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
+          <t>세로 : 134 가로 : 54</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>부부의 초상화 중 남편을 그린 그림. 화폭(세로 91.7, 가로 34). 정자관에 흰색 두루마기를 입고, 서양식 의자에 앉아 있는 모습을 그린 것임. 좌측상단에는 '本貫 永川 壬寅二月初六日 生 李寧澤 影像 辛卯年 漢陽居士 朴松坡'가 묵서됨. 좌측하단에는 낙관 '漢陽居士 朴松坡款'이 찍혀 있음. 전통방식의 초상화를 근대 서양화법으로 제작. 그림용 화견(畵絹)이 아닌 일반옷감에 그렸고, 장황은 종이로 꾸밈. 벽에 걸기 위해 족자 상축에는 2개의 구멍을 뚫고, 실을 엮어 걸 수 있게 만듦. 40455-40456 한 조임.</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
           <t>PS0100200100104045500000</t>
         </is>
       </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4750,8 +5864,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D79" t="n">
-        <v>40456</v>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>40456</t>
+        </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -4772,19 +5888,31 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8357056.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8357056.do; https://www.nfm.go.kr/common/apiimage/relic/8357055.do; https://www.nfm.go.kr/common/apiimage/relic/8357054.do; https://www.nfm.go.kr/common/apiimage/relic/8357057.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
+          <t>세로 : 134 가로 : 54</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>부부의 초상화 중 부인을 그린 그림. 화폭(세로 91.7, 가로 34). 흰색 저고리와 치마를 입고, 서양식 의자에 앉아 있는 모습을 그린 것임. 좌측상단에는 '本貫 文化 柳氏 丙午十一月 十九日生 辛卯表題畵像'이 묵서됨. 좌측하단에는 낙관 '漢陽居士 朴松坡款'이 찍혀 있음. 전통방식의 초상화를 근대 서양화법으로 제작. 그림용 화견(畵絹)이 아닌 일반 옷감에 그렸고, 장황은 종이로 꾸밈. 벽에 걸기 위해 족자 상축에는 2개의 구멍이 뚫려 있고, 실을 엮어 걸 수 있게 되어 있음. 40455-40456 한 조임.</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
           <t>PS0100200100104045600000</t>
         </is>
       </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4802,8 +5930,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D80" t="n">
-        <v>40438</v>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>40438</t>
+        </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -4828,19 +5958,31 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8367916.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8367916.do; https://www.nfm.go.kr/common/apiimage/relic/8367921.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
+          <t>세로 : 156.5 가로 : 80.6</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>평양 기생 계월향(桂月香·?~1592)을 그린 초상화. 그림 상단에는 '의기 계월향(義妓 桂月香)'이라는 제목의 제발이 적여 있음. 화면(세로 112.0, 가로 61.2) 지본채색(紙本彩色). 머리에는 가채를 쓰고, 녹색 저고리에 치마를 입고, 화문석 위에 앉아 있는 모습을 그림. 왼손에는 검은색 띠를 쥐고 있음</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
           <t>PS0100200100104043800000</t>
         </is>
       </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4858,8 +6000,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D81" t="n">
-        <v>39717</v>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>39717</t>
+        </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -4884,19 +6028,31 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8537945.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8537945.do</t>
+          <t>문화예술-서화-회화</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
+          <t>가로 : 64 세로 : 100</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>민영휘(閔泳徽, 1852~1935)의 34세 때 초상화. 지본채색(紙本彩色). 화폭(세로 98, 가로62). 청색 단령에 쌍학문 흉배와 각대(角帶), 사모를 착용한 전신 좌상(全身坐像). 화면 왼쪽 상단에 '藥山府伯閔泳駿 時年三十四 乙酉菊月上澣'이 적혀 있음. 영준(泳駿)은 초명임. 민화풍으로 화면 오른쪽에 꽃이 그려져 있음.</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
           <t>PS0100200100103971700000</t>
         </is>
       </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4914,8 +6070,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D82" t="n">
-        <v>45479</v>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>45479</t>
+        </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -4940,19 +6098,31 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8549292.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8549292.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
+          <t>세로 : 160 가로 : 75</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>문관(文官)을 그린 그림. 족자. 견본채색(絹本彩色). 화폭(세로 143, 가로 67.7). 쌍학흉배(雙鶴胸背)를 부착한 단령에 사모(紗帽)와 서대(犀帶)를 착용하고 의자에 앉아 있는 전신좌상. 의자에는 호피가, 족좌대(足座臺)에는 화문석이 깔려 있음. 배경에는 소병(素屛)이 배치됨. 화면에 가로·세로로 꺾인 자국이 있고, 안료는 군데군데 박락됨. 화면 우측 상단 한 곳에 구멍이 나 있음. 우측 상단 표장비단 부분에 일부 종이가 붙어 있음. 상축 윗면 좌우 양쪽에 족자 고리 있음.</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
           <t>PS0100200100104547900000</t>
         </is>
       </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4970,8 +6140,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D83" t="n">
-        <v>39716</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>39716</t>
+        </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -4996,19 +6168,31 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8355326.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8355326.do</t>
+          <t>문화예술-서화-회화</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
+          <t>세로 : 116 가로 : 72.5</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>흑건(黑巾)에 녹포(綠袍)를 입은 모습의 전신좌상(全身坐像). 족자형. 견본채색(絹本彩色). 화폭(세로 93, 가로 67). 오른손에 홀을 쥐고 있고, 왼손으로는 수염을 만지고 있는 모습임.</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
           <t>PS0100200100103971600000</t>
         </is>
       </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5026,8 +6210,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D84" t="n">
-        <v>57821</v>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>57821</t>
+        </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -5052,19 +6238,31 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8373940.do</t>
+          <t>한국-일제강점</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8373940.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
+          <t>가로 : 94.7 세로 : 165.5</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>인물의 전신상(全身像)을 그린 그림. 액자 형태. 지본수묵채색(紙本水墨彩色). 화폭(세로 125.6, 가로 75.8). 포와 전복을 입고 정자관을 쓴 인물이 의자에 앉아 있는 모습을 그림.</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
           <t>PS0100200100105782100000</t>
         </is>
       </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5082,8 +6280,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D85" t="n">
-        <v>47163</v>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>47163</t>
+        </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -5108,19 +6308,31 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8363190.do</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8363190.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
+          <t>세로 : 132.3 가로 : 90</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>정자관(程子冠)에 포(袍)를 입은 남성이 바닥에 화문석 돗자리를 깔고 앉은 부좌상(趺坐像). 액자 형태로, 유리가 끼워져 있음. 견본채색(絹本彩色). 화폭(세로 96, 가로 60). 인물 주위로 문방구류, 서책, 찻잔세트, 머릿장 등이 배치되고, 머릿장이나 나전함, 연대(硯臺) 등의 문양은 세밀하게 표현됨. 액자 뒷면 상단 좌우에 투명 튜브로 감싸진 와이어줄 있음.</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
           <t>PS0100200100104716300000</t>
         </is>
       </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5138,8 +6350,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D86" t="n">
-        <v>103484</v>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>103484</t>
+        </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -5164,19 +6378,31 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8608917.do</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8608917.do; https://www.nfm.go.kr/common/apiimage/relic/8608916.do; https://www.nfm.go.kr/common/apiimage/relic/8608919.do; https://www.nfm.go.kr/common/apiimage/relic/8608918.do; https://www.nfm.go.kr/common/apiimage/relic/8608920.do</t>
+          <t>사회생활-의례생활-상장-상장문서</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
+          <t>세로 : 15.5 가로 : 21.1 두께 : 0.4</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>문상객을 기록한 방명록. 1책. 가철(假綴). 필사본(筆寫本). 표지 2장. 내지 6장. 병자년(丙子) 7월 7일 작성. 조문객의 이름과 부의 내용이 기재됨. 초상(初喪)에 참석한 인물이 기재됨.</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
           <t>PS0100200100110348400000</t>
         </is>
       </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5194,8 +6420,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D87" t="n">
-        <v>103730</v>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>103730</t>
+        </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -5220,19 +6448,31 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8607829.do</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8607829.do; https://www.nfm.go.kr/common/apiimage/relic/8607830.do</t>
+          <t>사회생활-의례생활-제례</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
+          <t>가로 : 112.5 세로 : 53.2</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>집안에서 초상(初喪)을 치를 때 순서와 업무를 분장(分掌) 한 문서. 임오년(壬午) 4월 5월 작성. 호상(護喪), 상례(相禮), 돈장(敦匠), 조빈(造殯), 사서(司書), 사화(司貨)로 나누어 각각 역할과 집사자의 이름이 기재됨.</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
           <t>PS0100200100110373000000</t>
         </is>
       </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5250,8 +6490,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D88" t="n">
-        <v>37544</v>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>37544</t>
+        </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -5276,19 +6518,31 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8352005.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8352005.do</t>
+          <t>미디어-아카이브-사진기록 / 문화예술-서화-회화</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
+          <t>세로 : 29.5 가로 : 23</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>콧수염을 기르고 검정색 두루마기를 입은 노인의 모습을 그린 영정용 초상화(세로 24, 가로 18). 액자형. 기존 사진에 그림을 덧그려 완성한 형태. 37544-37545 한 조임.</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
           <t>PS0100200100103754400000</t>
         </is>
       </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5306,8 +6560,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D89" t="n">
-        <v>103726</v>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>103726</t>
+        </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -5332,19 +6588,31 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8606768.do</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8606768.do; https://www.nfm.go.kr/common/apiimage/relic/8606769.do</t>
+          <t>사회생활-의례생활-제례</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
+          <t>세로 : 50 가로 : 88</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>집안에서 초상(初喪)을 치를 때 순서와 업무를 분장(分掌)한 문서. 임진년(壬辰) 1월 7일 작성. 호곡(護哭), 상례(相禮), 축(祝), 진설(陳設), 돈장(敦匠), 조빈(造殯), 사서(司書), 사화(司貨)로 나누어 각각 역할과 집사자의 이름이 기재됨.</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
           <t>PS0100200100110372600000</t>
         </is>
       </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5362,8 +6630,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D90" t="n">
-        <v>37545</v>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>37545</t>
+        </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -5388,19 +6658,31 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8353809.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8353809.do</t>
+          <t>문화예술-서화-회화 / 미디어-아카이브-사진기록</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
+          <t>세로 : 29.5 가로 : 23.3</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>'壽'자문이 수 놓여진 두루마기를 입은 여성 노인의 모습을 그린 영정용 초상화(세로 23, 가로 18). 액자형. 기존 사진에 그림을 덧그려 완성한 형태. 37544-37545 한 조임.</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
           <t>PS0100200100103754500000</t>
         </is>
       </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5418,8 +6700,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D91" t="n">
-        <v>45478</v>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>45478</t>
+        </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -5444,19 +6728,31 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8557482.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8557482.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
+          <t>가로 : 150 세로 : 98.5</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>조선 말기 무관 조희복(趙羲復)을 그린 그림. 액자 형태로, 유리가 끼워져 있음. 견본채색(絹本彩色). 화폭(세로 120.5, 가로 77.2). 쌍호흉배(雙虎胸背)를 부착한 단령에 사모(紗帽)와 학정금대(鶴頂金帶)를 착용하고, 부채를 들고 의자에 앉아 있는 전신좌상. 몸체 비례가 맞지 않음. 의자에는 호피가, 족좌대(足座臺)와 바닥에는 화문석이 깔려 있음. 배경에는 일부 접혀있는 산수 병풍이 배치되고, 화면 가장자리에는 테두리가 둘러짐. 좌측 및 하단 일부와 우측 가장자리에 종이가 덧대지고, 우측에는 '判書趙公○羲復之眞影'가 묵서됨. 액자로 개장(改裝)됨. 액자 뒷면 상단부 좌우측에 각각 와이어 고리 달림.</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
           <t>PS0100200100104547800000</t>
         </is>
       </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5474,8 +6770,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D92" t="n">
-        <v>83998</v>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>83998</t>
+        </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -5500,19 +6798,31 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8451894.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8451894.do; https://www.nfm.go.kr/common/apiimage/relic/8451895.do</t>
+          <t>문화예술-서화-회화</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
+          <t>세로 : 113.5 가로 : 67.5</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>화가 석지 채용신(蔡龍臣, 1848-1941)이 그린 초상화(肖像畫). 1919년 작(作). 견본채색(絹本彩色). 산수도(山水圖) 병풍 앞에 가부좌를 한 인물이 그려짐. 인물 오른손에 부채가 들려있고 허리에 달린 호패에 생몰년(生歿年)이 간지로 표현됨. 병풍에는 '己未冬石芝'가 묵서되고 채용신의 낙관(落款)이 찍혀 있음.</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
           <t>PS0100200100108399800000</t>
         </is>
       </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5530,8 +6840,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D93" t="n">
-        <v>51676</v>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>51676</t>
+        </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -5556,19 +6868,31 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8368252.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8368252.do</t>
+          <t>문화예술-서화-회화-서양화</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
+          <t>세로 : 44 가로 : 35.5</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>김언석 부친(김흥태)의 초상화(영정). 1975년 제작. 앞면에 유리가 끼워진 형태. 캔버스(canvas)에 채색. 화폭(세로 38, 가로 29). 캔버스 가장자리를 비단으로 표장(表裝)함. 액자틀 뒷면 상단 중앙에 액자걸이가 달림. 캔버스와 액자틀 옆면과 뒷면에 쇠못이 박힘. 화면 우측 하단에 '75.PARK.S.K' 제작년도와 작가 사인이 적힘.</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
           <t>PS0100200100105167600000</t>
         </is>
       </c>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5586,8 +6910,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D94" t="n">
-        <v>51677</v>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>51677</t>
+        </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -5612,19 +6938,31 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8394614.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8394614.do</t>
+          <t>문화예술-서화-회화-서양화</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
+          <t>가로 : 35.5 세로 : 44</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>김언석 모친(박광숙)의 초상화(영정). 1975년 제작. 앞면에 유리가 끼워진 형태. 캔버스(canvas)에 채색. 화폭(세로 38, 가로 29). 캔버스 가장자리를 비단으로 표장(表裝)함. 액자틀 뒷면 상단 중앙에 액자걸이가 달림. 캔버스와 액자틀 옆면과 뒷면에 쇠못이 박힘. 화면 우측 하단에 '75.PARK.S.K' 제작년도와 작가 사인이 적힘.</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
           <t>PS0100200100105167700000</t>
         </is>
       </c>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5642,8 +6980,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D95" t="n">
-        <v>103710</v>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>103710</t>
+        </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -5668,19 +7008,31 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8605721.do</t>
+          <t>한국-일제강점</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8605721.do; https://www.nfm.go.kr/common/apiimage/relic/8605722.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
+          <t>가로 : 60 세로 : 197</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>부부의 초상화 중 남편을 그린 그림. 족자. 견본채색(絹本彩色). 화폭(세로 104.5, 가로 42). 정자관에 흰색 두루마기를 입고, 한 손에 부채를 들고 서양식 의자에 앉아 있는 모습. 좌측 하단에는 '臥牛山人錦島 癸未九月中旬' 묵서되고 낙관(落款) 찍혀 있음. 족자 상하단은 비단으로 장황(裝潢) 됨. 상축 축목에 족자 고리못과 꽃 모양의 고리 장식이 있고, 족자 끈과 유소(流蘇)가 달려 있음.</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
           <t>PS0100200100110371000000</t>
         </is>
       </c>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5698,8 +7050,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D96" t="n">
-        <v>103711</v>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>103711</t>
+        </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -5724,19 +7078,31 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8605724.do</t>
+          <t>한국-일제강점</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8605724.do; https://www.nfm.go.kr/common/apiimage/relic/8605723.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
+          <t>세로 : 197 가로 : 62</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>부부의 초상화 중 부인을 그린 그림. 족자. 견본채색(絹本彩色). 화폭(세로 104.5, 가로 42). 흰색 치마저고리를 입고, 두 손을 모으고 서양식 의자에 앉아 있는 모습. 좌측 하단에는 '臥牛山人錦島 癸未九月中旬' 묵서 되고 낙관(落款) 찍혀 있음. 족자 상하단은 비단으로 장황(裝潢) 됨. 상축 축목에 족자 고리못과 꽃 모양의 고리 장식이 있고, 족자 끈과 유소(流蘇)가 달려 있음.</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
           <t>PS0100200100110371100000</t>
         </is>
       </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5754,8 +7120,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D97" t="n">
-        <v>40459</v>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>40459</t>
+        </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -5780,19 +7148,31 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8541958.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8541958.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
+          <t>가로 : 53.5 높이 : 85</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>오사모(烏紗帽)에 분홍색 단령(團領)을 입은 반신상 초상화 초본(草本) .액자형. 지본담채(紙本淡彩). 화폭(세로 54, 가로 30). 조선 후기 인물, 강유(姜游)를 그린 그림이라고 전해짐.</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
           <t>PS0100200100104045900000</t>
         </is>
       </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5810,8 +7190,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D98" t="n">
-        <v>78562</v>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>78562</t>
+        </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -5832,19 +7214,31 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8457595.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8457595.do; https://www.nfm.go.kr/common/apiimage/relic/8457594.do</t>
+          <t>미디어-아카이브-사진기록-사진</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
+          <t>세로 : 47.5 가로 : 37.3</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>이명래 선생의 초상화 액자. 직사각 형태로, 앞면에 유리가 끼워짐.</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
           <t>PS0100200100107856200000</t>
         </is>
       </c>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5862,8 +7256,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D99" t="n">
-        <v>81050</v>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>81050</t>
+        </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -5888,19 +7284,31 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8463619.do</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8463619.do</t>
+          <t>문화예술-서화-회화-기타</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
+          <t>세로 : 109 가로 : 73</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>보천교(普天敎)의 창시자인 차경석(車京石)의 모습을 그린 초상화(肖像畵). 지본채색(紙本彩色). 정자관을 쓰고 도포를 입은 차경석이 의자에 앉아있는 모습으로 그려짐. 차경석의 뒤에 병풍이 둘려있음. 좌측 하단에 도장 1과(顆) 찍혀있음.</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
           <t>PS0100200100108105000000</t>
         </is>
       </c>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5918,8 +7326,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D100" t="n">
-        <v>99725</v>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>99725</t>
+        </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -5944,19 +7354,31 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8491288.do</t>
+          <t>한국-일제강점</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8491288.do; https://www.nfm.go.kr/common/apiimage/relic/8491292.do; https://www.nfm.go.kr/common/apiimage/relic/8491291.do; https://www.nfm.go.kr/common/apiimage/relic/8491289.do; https://www.nfm.go.kr/common/apiimage/relic/8491290.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
+          <t>세로 : 58 가로 : 41.5 두께 : 2</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>부부의 모습이 각각 그려진 초상화. 2개의 액자로 구성됨. 종이에 소묘(素描). 화폭(세로47.5, 가로 33). 인물과 잔치상이 묘사됨. 부인의 모습 뒤쪽에 송학도 병풍이 그려지고, 왼쪽 상단에 '拀 昭和十四年二月二十日' 이 적혀 있음.</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
           <t>PS0100200100109972500000</t>
         </is>
       </c>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5974,8 +7396,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D101" t="n">
-        <v>30875</v>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>30875</t>
+        </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -6000,19 +7424,31 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8553538.do</t>
+          <t>한국-대한제국</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8553538.do</t>
+          <t>문화예술-서화-회화</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
+          <t>가로 : 111 세로 : 232.5</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>한말(韓末)의 문신이자 정치가인 이용익(李容翊, 1854~1907)의 초상을 그린 그림. 견본채색(絹本彩色). 족자형(세로 312, 가로 124.7). 서양식 제복을 입고 서 있는 모습을 그린 전신초상화(全身肖像畵)임. 가슴에는 3개의 훈장이 달려 있고, 왼손에는 예도(銳刀)를 들고 있음.</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
           <t>PS0100200100103087500000</t>
         </is>
       </c>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6030,8 +7466,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D102" t="n">
-        <v>1</v>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -6052,19 +7490,31 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8292746.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8292746.do; https://www.nfm.go.kr/common/apiimage/relic/8292747.do</t>
+          <t>문화예술-서화-회화-서양화</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
+          <t>가로 : 23 세로 : 32</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>서울대에 다니던 제자가 그려준 송석하 선생의 초상화. 지본채색. 유화. 얼굴은 검은 색 계통으로 전체적인 윤곽만을 강조하였기 때문에 선명하지 못함. 바탕은 녹색 계통임.</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
           <t>PS0100200100300000100000</t>
         </is>
       </c>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6082,8 +7532,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D103" t="n">
-        <v>40224</v>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>40224</t>
+        </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -6108,19 +7560,31 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8548708.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8548708.do; https://www.nfm.go.kr/common/apiimage/relic/8548707.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
+          <t>가로 : 65 세로 : 111.3</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>1882년(고종19) 무위대장을 역임한 이경하(李景夏, 1811~1891)의 초상화. 족자형. 견본채색(絹本彩色). 화폭(세로 74, 가로 57.3). 사모에서 흉배까지 그린 반신상. 머리에는 오사모(烏紗帽)를 쓰고, 짙은 녹색을 띤 검정색 운보문단령(雲寶紋團翎)을 입고 있으며, 가슴에는 쌍호흉배를 착용하고, 각대(角帶)를 둘렀음. 우측상단에 신미년(1871)에 쓴 자찬이 쓰여 있고, 백문방인이 찍혀 있음.</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
           <t>PS0100200100104022400000</t>
         </is>
       </c>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6138,8 +7602,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D104" t="n">
-        <v>81047</v>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>81047</t>
+        </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -6164,19 +7630,31 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8463195.do</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8463195.do; https://www.nfm.go.kr/common/apiimage/relic/8463194.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
+          <t>세로 : 149.5 가로 : 88.5</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>백각 강현(白閣 姜鋧)의 모습을 그린 초상화(肖像畫). 임모본(臨摸本). 액자 형태. 견본채색(絹本彩色). 화폭(세로 115, 가로 72). 쌍학흉배(雙鶴胸背)를 부착한 단령에 사모(紗帽)와 혁대를 착용하고, 두 손을 모으고 의자에 앉아 있는 전신 좌상. 두 발은 족좌대(足座臺)에 올려놓음. 의자에는 호피 둘려있음. 화면 주위는 비단으로 장황(裝潢)됨. 뒷면에 보천교(普天敎) 부적 1개 부착됨.</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
           <t>PS0100200100108104700000</t>
         </is>
       </c>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6194,8 +7672,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D105" t="n">
-        <v>70306</v>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>70306</t>
+        </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -6216,19 +7696,31 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8591275.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8591275.do</t>
+          <t>문화예술-서화-회화</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
+          <t>세로 : 136 가로 : 95.5</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>스님의 모습을 그린 초상화. 액자형태. 견본채색(絹本彩色). 화폭(세로 107.5, 가로 77.5). 화면 중앙에 스님이 결가부좌(結跏趺坐)한 모습이 그려짐. 스님은 녹색의 장삼(長衫)에 홍색 가사(架裟)를 걸치고 주장자(拄杖子)와 염주(念珠)를 들고 있음. 좌측 상단에 ˈ樿敎兩宗觧庵堂信忍之真相ˈ이 묵서되고, 상단 좌우측에 영찬(影讚)이 적혀 있음. 우측 영찬 끝에 주문방인(朱文方印)이 찍혀 있음. 화면 주위는 비단으로 장황(裝潢)됨. 뒷면 상단에 액자 걸이 달림.</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
           <t>PS0100200100107030600000</t>
         </is>
       </c>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6246,8 +7738,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D106" t="n">
-        <v>93350</v>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>93350</t>
+        </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -6272,19 +7766,31 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8481121.do</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8481121.do; https://www.nfm.go.kr/common/apiimage/relic/8481122.do</t>
+          <t>문화예술-서화-회화-기타</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
+          <t>세로 : 144 가로 : 83</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>한용직(韓用稷)을 그린 초상화. 족자형태. 견본채색(絹本彩色). 화폭(세로 121.5, 가로 71). 쌍호 흉배(雙虎 胸背)의 문관복(文官服)을 착용한 인물이 의자에 앉아 있는 전신좌상. 바닥에는 화문석이 깔려 있고 중앙에 인장함(印章函)이 놓여 있음. 좌측 상단에 '三昧抄形全是假七', '分移貌完其真', '門人韓用直謹撰'이 묵서됨. 족자 옆단과 상,하단 비단으로 장황(裝潢)됨. 상단에 유소 2개 늘어뜨림. 반달에 고리 2개가 달리고 족자끈이 연결됨.</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
           <t>PS0100200100109335000000</t>
         </is>
       </c>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6302,8 +7808,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D107" t="n">
-        <v>99723</v>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>99723</t>
+        </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -6328,19 +7836,31 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8491286.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8491286.do; https://www.nfm.go.kr/common/apiimage/relic/8491283.do; https://www.nfm.go.kr/common/apiimage/relic/8491281.do; https://www.nfm.go.kr/common/apiimage/relic/8491284.do; https://www.nfm.go.kr/common/apiimage/relic/8491287.do; https://www.nfm.go.kr/common/apiimage/relic/8491282.do; https://www.nfm.go.kr/common/apiimage/relic/8491280.do; https://www.nfm.go.kr/common/apiimage/relic/8491285.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
+          <t>두께 : 6.7 세로 : 144.5 가로 : 67</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>조선시대 무관의 초상을 그린 그림. 양문형 액자에 족자가 걸려 있는 형태. 캔버스(canvas)에 유채. 화면에는 인물의 전신이 배치됨. 3품 이하의 당하관을 상징하는 단호문흉배(單虎紋胸背)가 수(繡) 놓인 녹색 관복과 사모를 착용하고, 등받이가 있는 교의자에 앉아 정면을 응시하고 있는 모습임. 화면 왼쪽 상단에 '崇禎五回甲子淸和節嶺霽權相行謹撰 書'가, 오른쪽 상단에는 '賛日 七分影一幅圖生绡鳥之動色 罒方志六旬齒風采恍若手神 爲袍烏帽認是舊代朝班 彩毫龍眼難畵今日儒迹 仁善爲基 剛倬其志 誰其眞體 吾友晩松'이 적혀 있음. 인물 뒤쪽으로 매작도와 송학도 병풍이 그려짐.</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
           <t>PS0100200100109972300000</t>
         </is>
       </c>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6358,8 +7878,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D108" t="n">
-        <v>75169</v>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>75169</t>
+        </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -6384,19 +7906,31 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8442113.do</t>
+          <t>한국-일제강점</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8442113.do</t>
+          <t>문화예술-서화-회화</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
+          <t>세로 : 95 가로 : 66</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>동초 김석곤(東樵 金晳坤)의 모습을 그린 초상화(肖像畫). 석지 채용신(石芝 蔡龍臣, 1848-1941) 작(作). 1918년 제작. 액자 형태. 견본채색(絹本彩色). 화폭(세로 74.5, 가로 46). 산수(山水)를 배경으로, 삿갓을 쓰고 도포(道袍)를 입은 김석곤이 돌 위에 앉아 있는 모습이 그려짐. 좌측 돌 사이에 붓이 그려짐. 우측 상단에 ˈ東樵居士金晳坤笠後肖像ˈ이 묵서되고, 좌측 상단에 1918년(戊午) 김석곤이 쓴 찬(撰)이 있고, ˈ東樵ˈ, ˈ石芝ˈ 등 주문방인(朱門方印) 3과(顆)와 ˈ金晳坤ˈ 등 백문방인(白文方印) 2과가 찍혀 있음. 화면 주위는 비단으로 장황(裝潢)됨.</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
           <t>PS0100200100107516900000</t>
         </is>
       </c>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6414,8 +7948,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D109" t="n">
-        <v>78854</v>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>78854</t>
+        </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -6436,19 +7972,31 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8471283.do</t>
+          <t>한국-일제강점</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8471283.do; https://www.nfm.go.kr/common/apiimage/relic/8471284.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
+          <t>가로 : 120.5 세로 : 140.5</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>조선 말기 화가 채용신(蔡龍臣, 1850~1941) 부부가 의자에 앉은 모습이 묘사된 초상화. 액자 형태. 그림은 족자 형태. 지본채색(紙本彩色). 화폭(세로 120, 가로 102). 좌측에 아내가, 우측에 남편이 그려짐. 아내는 가락지를 낀 왼손을 오른손 위로 포개어 무릎 위에 두고, 남편은 정자관을 쓰고 부채와 안경을 양손에 쥔 모습임. 바닥에 대자리가, 배경에 병풍이 그려짐. 병풍 좌측 하단에 '壬申十二月從二品蔡石芝九十翁寫'가 묵서됨.</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
           <t>PS0100200100107885400000</t>
         </is>
       </c>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6466,8 +8014,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D110" t="n">
-        <v>39650</v>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>39650</t>
+        </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -6492,19 +8042,31 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8524148.do</t>
+          <t>한국-일제강점</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8524148.do; https://www.nfm.go.kr/common/apiimage/relic/8524147.do; https://www.nfm.go.kr/common/apiimage/relic/8524146.do</t>
+          <t>문화예술-서화-회화</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
+          <t>가로 : 91 세로 : 187</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>한의사 조철승(曺喆承, 1849~?)의 42세 때 초상화. 족자형. 견본채색(絹本彩色). 화폭(세로 162, 가로 75). 정자관(程子冠)에 도포를 입고 청색 세조대(細條帶)를 착용한 전신좌상(全身坐像).『잡병제강(雜病堤綱)』이라는 의학서를 오른손에 들고 있음. 이 작품은 원효사 화승(畵僧)인 징헌(登彦)이 경인년(庚寅年:1890년)에 그린 그림을 병진년(丙辰年:1916년)에 최병육(崔丙六)이 다시 모사한 것임. 그림 상단 좌우에 인물에 대한 인적 사항과 그림에 대한 기록이 있음. 인물 주변에 책, 붓 등 문방도 도상이 그려져 있음.</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
           <t>PS0100200100103965000000</t>
         </is>
       </c>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6522,8 +8084,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D111" t="n">
-        <v>81401</v>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>81401</t>
+        </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -6548,19 +8112,31 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8458895.do</t>
+          <t>한국-대한제국</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8458895.do; https://www.nfm.go.kr/common/apiimage/relic/8458893.do; https://www.nfm.go.kr/common/apiimage/relic/8458894.do</t>
+          <t>문화예술-서화-회화-기타</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
+          <t>가로 : 75 세로 : 144</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>조선 말기 문관을 그린 초상화. 석지(石芝) 채용신(蔡龍臣, 1850~1941) 작(作). 족자형태. 견본채색(絹本彩色). 화폭(세로 113, 가로 66). 단학흉배(單鶴胸背)의 문관복(文官服)을 착용한 인물이 의자에 앉아 있는 전신좌상. 오른손에 부채를 쥐고 있고 허리에 달린 호패에는 '巳酉生(사유생) 癸卯入仕(계묘입사)'가 적혀 있음. 바닥에는 화문석이 깔려 있음. 화면 좌측 중앙에 주문방인(朱文方印)이 찍혀 있음. 화폭 위아래는 장황(裝潢)됨. 상단에 유소 2개 늘어뜨림. 반달에 고리 2개가 달리고 족자끈이 연결됨. 아크릴 액자에 보관됨.</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
           <t>PS0100200100108140100000</t>
         </is>
       </c>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6578,8 +8154,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D112" t="n">
-        <v>37543</v>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>37543</t>
+        </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -6604,19 +8182,31 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8537907.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8537907.do</t>
+          <t>문화예술-서화-회화-서양화</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
+          <t>가로 : 64 세로 : 72</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>문관(文官)복장을 한 남자의 모습을 그린 그림(세로 51, 가로 43.5). 캔버스(canvas)에 유채(油彩). 윤필구(尹弼九) 작(作). 액자형. 화폭 오른쪽에 ‘嘉善大夫竹史徐公之像’이라고 적혀 있음. 그림의 뒷면에 ‘1969. 10. 6 眞影에 依하여 尹弼九 謹寫’, ‘子 丙七’이라고 적혀 있음. 전통 기법으로 그려진 원본을 베껴 유화로 그렸음.</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
           <t>PS0100200100103754300000</t>
         </is>
       </c>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6634,8 +8224,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D113" t="n">
-        <v>39654</v>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>39654</t>
+        </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -6660,19 +8252,31 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8357693.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8357693.do; https://www.nfm.go.kr/common/apiimage/relic/8357692.do; https://www.nfm.go.kr/common/apiimage/relic/8357694.do</t>
+          <t>문화예술-서화-회화</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
+          <t>세로 : 141 가로 : 81.5</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>정자관(程子冠)에 흰색도포를 입고 녹색 세조대(細條帶)를 두르고 의자에 앉아 있는 전신좌상(全身坐像). 족자형. 마본채색(麻本彩色). 화폭(세로 124, 가로 74.5). 그림 윗부분에는 청색 휘장이, 바닥에는 화문석이 그려져 있음.</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
           <t>PS0100200100103965400000</t>
         </is>
       </c>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6690,8 +8294,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D114" t="n">
-        <v>70307</v>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>70307</t>
+        </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -6716,19 +8322,31 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8448072.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8448072.do</t>
+          <t>문화예술-서화-회화</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
+          <t>세로 : 45.5 가로 : 36.5</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>인물의 얼굴이나 모습을 그린 그림. 액자형태. 견본채색(絹本彩色). 화폭(세로 28, 가로 19). 정자관(程子冠)에 도포를 입고 있는 모습을 그린 반신상(半身像). 상단에 ˈ通政大夫行 承政院 右副承旨兼經筵參贊官繡山申公用珣三十五歲真ˈ이 적혀 있음. 우측 상단에 1895년(乙未)에 적은 찬(撰)이 있고, 백문방인(白文方印)과 주문방인(朱文方印) 이 찍혀 있음. 화면 주위는 비단으로 장황(裝潢)됨. 뒷면 상단 좌우에 액자걸이 부착되고 끈이 달려 있음. 뒷면 하단 좌측에 ˈPeinture coreenne portrait dˈun mandarin collection Collin de Plancyˈ이 적혀 있음.</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
           <t>PS0100200100107030700000</t>
         </is>
       </c>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6746,8 +8364,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D115" t="n">
-        <v>45862</v>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>45862</t>
+        </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -6772,19 +8392,31 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8561513.do</t>
+          <t>한국-일제강점</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8561513.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
+          <t>가로 : 58 세로 : 118</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>윤씨조모(尹氏祖母)를 그린 그림. 석지 채용신(石芝 蔡龍臣, 1850~1941) 작(作). 족자. 견본채색(絹本彩色). 화폭(세로 98.5, 가로 54.6). 3폭의 산수 병풍을 배경으로, '壽'자문이 그려진 흰색 치마저고리를 입고, 가슴에는 노리개와 단도를 달고 있는 전신좌상. 얼굴, 머리, 목 부분은 종이를 덧붙인 후 그려지고, 손에는 일부 수정 흔적 있음. 족자 상하단은 비단으로 표장(表裝)됨. 상축에 족자고리못과 꽃모양의 고리장식이 있고, 족자끈과 유소(流蘇)가 달려 있음. 뒷면 좌측 상단에 '甲寅年生尹氏祖母象 石芝蔡龍臣'이 묵서된 붉은색 별지가 붙어 있고, 보호지로 덮여 있음.</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
           <t>PS0100200100104586200000</t>
         </is>
       </c>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6802,8 +8434,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D116" t="n">
-        <v>15295</v>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>15295</t>
+        </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -6828,19 +8462,31 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8389174.do</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8389174.do; https://www.nfm.go.kr/common/apiimage/relic/8389176.do; https://www.nfm.go.kr/common/apiimage/relic/8389175.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
+          <t>가로 : 66.5 세로 : 42</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>평양조씨(平壤趙氏) 집안의 첫째 조계(趙啓 - '啓'字의 '口'대신 '山'이 들어간 글자를 만들어 사용함), 둘째 조두(趙㞳), 셋째 조강(趙岡) 삼형제를 그린 그림임.</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
           <t>PS0100200100101529500000</t>
         </is>
       </c>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6858,8 +8504,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D117" t="n">
-        <v>63742</v>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>63742</t>
+        </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -6884,19 +8532,31 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8240104.do</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8240104.do</t>
+          <t>종교신앙</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
+          <t>가로 : 132.5 세로 : 147</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>증산교(甑山敎) 창시자 강일순(姜一淳, 1871~1909)을 그린 그림. 종이에 사직(絲織)을 붙이고 그 위에 그림을 그린 형태. 도포를 입고 5층 정자관을 쓴 인물이 연꽃 대좌에 서 있음. 광배와 백호(白毫)가 있음. 오른손은 엄지와 검지를, 왼손은 엄지와 중지를 붙인 형태의 수인(手印)을 하고 있음. 인물 양측에 목패가 있음.</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
           <t>PS0100200100106374200000</t>
         </is>
       </c>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6914,8 +8574,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D118" t="n">
-        <v>78327</v>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>78327</t>
+        </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -6936,19 +8598,31 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8461428.do</t>
+          <t>한국-광복이후</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8461428.do; https://www.nfm.go.kr/common/apiimage/relic/8461427.do</t>
+          <t>문화예술-서화-회화-서양화</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
+          <t>세로 : 27.3 가로 : 24.2</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>움직이는 사람이나 사물의 형태를 빠르게 그린 그림. 현민 유진오(玄民 兪鎭午)의 얼굴임.</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
           <t>PS0100200100107832700000</t>
         </is>
       </c>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6966,8 +8640,10 @@
           <t>국립민속박물관</t>
         </is>
       </c>
-      <c r="D119" t="n">
-        <v>37540</v>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>37540</t>
+        </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -6992,19 +8668,31 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8537619.do</t>
+          <t>한국-일제강점</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8537619.do; https://www.nfm.go.kr/common/apiimage/relic/8537616.do; https://www.nfm.go.kr/common/apiimage/relic/8537620.do; https://www.nfm.go.kr/common/apiimage/relic/8537615.do; https://www.nfm.go.kr/common/apiimage/relic/8537622.do; https://www.nfm.go.kr/common/apiimage/relic/8537618.do; https://www.nfm.go.kr/common/apiimage/relic/8537621.do; https://www.nfm.go.kr/common/apiimage/relic/8537617.do</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
+          <t>가로 : 73 세로 : 113.5 두께 : 7.5</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>추수(秋水) 김제덕(金濟悳, 1855~1925)의 초상화(세로 89, 가로 59). 비단에 채색. 석지(石芝) 채용신(蔡龍臣, 1850~1941) 작(作). 화폭 우측 상단에 ' 秋水翁六十七歲像', 좌측 하단에 '一千○十五萬五千八百三十八年辛酉小春上澣從二品前府使石芝八十翁寫'라고 적혀 있음. 영정은 표구되어 문이 달린 함에 보관됨. 함의 위 아래 머름칸에는 여의두문이 장식되고 문종이에는 국화문이 그려짐.</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
           <t>PS0100200100103754000000</t>
         </is>
       </c>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/nfm_merge.xlsx
+++ b/data/nfm_merge.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P119"/>
+  <dimension ref="A1:P88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,7 +692,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>세로 : 20.7 가로 : 20.6</t>
+          <t>가로 : 20.6 세로 : 20.7</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>가로 : 21.6 세로 : 22.8</t>
+          <t>세로 : 22.8 가로 : 21.6</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>가로 : 24 세로 : 25</t>
+          <t>세로 : 25 가로 : 24</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>가로 : 17.5 세로 : 19</t>
+          <t>세로 : 19 가로 : 17.5</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>가로 : 17.5 세로 : 19.7</t>
+          <t>세로 : 19.7 가로 : 17.5</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>의-의류-부분품-보/흉배 / 사회생활-의례생활-상장</t>
+          <t>사회생활-의례생활-상장 / 의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>너비 : 38 길이 : 37</t>
+          <t>길이 : 37 너비 : 38</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>가로 : 17.2 세로 : 18</t>
+          <t>세로 : 18 가로 : 17.2</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>세로 : 59 가로 : 59</t>
+          <t>가로 : 59 세로 : 59</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>길이 : 430 너비 : 104</t>
+          <t>너비 : 104 길이 : 430</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>화장 : 121 길이 : 126 품 : 54</t>
+          <t>품 : 54 화장 : 121 길이 : 126</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>화장 : 120.5 길이 : 125 품 : 57</t>
+          <t>화장 : 120.5 품 : 57 길이 : 125</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>의-의류-평상복-남자포류 / 사회생활-의례생활-상장</t>
+          <t>사회생활-의례생활-상장 / 의-의류-평상복-남자포류</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>길이 : 131.5 품 : 55 화장 : 125.5</t>
+          <t>품 : 55 길이 : 131.5 화장 : 125.5</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>화장 : 118 길이 : 136 품 : 50</t>
+          <t>길이 : 136 화장 : 118 품 : 50</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>사회생활-의례생활-상장 / 의-의류-평상복-남자포류</t>
+          <t>의-의류-평상복-남자포류 / 사회생활-의례생활-상장</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>길이 : 129.5 품 : 57 화장 : 127.5</t>
+          <t>품 : 57 길이 : 129.5 화장 : 127.5</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>길이 : 132 화장 : 127 품 : 59</t>
+          <t>품 : 59 화장 : 127 길이 : 132</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>품 : 56 길이 : 125 화장 : 114</t>
+          <t>화장 : 114 길이 : 125 품 : 56</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>화장 : 127.5 길이 : 138.5</t>
+          <t>길이 : 138.5 화장 : 127.5</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>등길이 : 124 품 : 50.5 화장 : 97.5</t>
+          <t>품 : 50.5 화장 : 97.5 등길이 : 124</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>화장 : 82 길이 : 125 품 : 57</t>
+          <t>길이 : 125 품 : 57 화장 : 82</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>화장 : 97 품 : 56 길이 : 123</t>
+          <t>품 : 56 길이 : 123 화장 : 97</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>길이 : 126.5 품 : 50 화장 : 89</t>
+          <t>품 : 50 화장 : 89 길이 : 126.5</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>품 : 52 화장 : 92 길이 : 121.5</t>
+          <t>길이 : 121.5 화장 : 92 품 : 52</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>길이 : 119.5 화장 : 87.5 품 : 45</t>
+          <t>길이 : 119.5 품 : 45 화장 : 87.5</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>화장 : 94 길이 : 116 품 : 46</t>
+          <t>길이 : 116 품 : 46 화장 : 94</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>화장 : 79 품 : 49.5 길이 : 120</t>
+          <t>품 : 49.5 길이 : 120 화장 : 79</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>품 : 47.5 화장 : 86 길이 : 121</t>
+          <t>길이 : 121 화장 : 86 품 : 47.5</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>품 : 59 길이 : 114 화장 : 99</t>
+          <t>화장 : 99 품 : 59 길이 : 114</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>길이 : 120 품 : 55 화장 : 82</t>
+          <t>길이 : 120 화장 : 82 품 : 55</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>길이 : 117.5 품 : 66 화장 : 130</t>
+          <t>길이 : 117.5 화장 : 130 품 : 66</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>길이 : 140.5 품 : 68 화장 : 122.5</t>
+          <t>품 : 68 화장 : 122.5 길이 : 140.5</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>화장 : 128.5 길이 : 124 품 : 74</t>
+          <t>품 : 74 화장 : 128.5 길이 : 124</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>등길이 : 123.5 품 : 57 화장 : 92</t>
+          <t>등길이 : 123.5 화장 : 92 품 : 57</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>화장 : 77.5 길이 : 126</t>
+          <t>길이 : 126 화장 : 77.5</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>품 : 50 화장 : 92 길이 : 124</t>
+          <t>품 : 50 길이 : 124 화장 : 92</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>길이 : 120 품 : 48 화장 : 69</t>
+          <t>품 : 48 화장 : 69 길이 : 120</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>길이 : 126 화장 : 85</t>
+          <t>화장 : 85 길이 : 126</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>품 : 57 등길이 : 123 화장 : 81</t>
+          <t>화장 : 81 등길이 : 123 품 : 57</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>화장 : 72 품 : 61 등길이 : 115</t>
+          <t>품 : 61 화장 : 72 등길이 : 115</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>화장 : 82 등길이 : 125 품 : 64</t>
+          <t>품 : 64 등길이 : 125 화장 : 82</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>화장 : 92.5 길이 : 130 품 : 49.5</t>
+          <t>화장 : 92.5 품 : 49.5 길이 : 130</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>등길이 : 126 품 : 50 화장 : 102.5</t>
+          <t>화장 : 102.5 품 : 50 등길이 : 126</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>품 : 68 화장 : 90 길이 : 133.5</t>
+          <t>길이 : 133.5 품 : 68 화장 : 90</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>화장 : 115 길이 : 124 품 : 71</t>
+          <t>길이 : 124 화장 : 115 품 : 71</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>화장 : 75 길이 : 127.5 품 : 58</t>
+          <t>화장 : 75 품 : 58 길이 : 127.5</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>길이 : 130 화장 : 89 진동 : 32</t>
+          <t>길이 : 130 진동 : 32 화장 : 89</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>길이 : 128 화장 : 87.5 품 : 62</t>
+          <t>화장 : 87.5 길이 : 128 품 : 62</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>품 : 56 화장 : 89.5 길이 : 124.2</t>
+          <t>화장 : 89.5 품 : 56 길이 : 124.2</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>길이 : 138.2 화장 : 92.5 품 : 61</t>
+          <t>화장 : 92.5 품 : 61 길이 : 138.2</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>품 : 57.5 화장 : 94.5 길이 : 98</t>
+          <t>화장 : 94.5 품 : 57.5 길이 : 98</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>가로 : 89.5 세로 : 151.5</t>
+          <t>세로 : 151.5 가로 : 89.5</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -5785,7 +5785,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>YNFMP03</t>
+          <t>YNFMP06</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5800,19 +5800,23 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>40455</t>
+          <t>39717</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>부부 초상화</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
+          <t>민영휘 초상</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>閔泳徽 肖像</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100104045500000</t>
+          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100103971700000</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5822,27 +5826,27 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>한국-광복이후</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>문화예술-서화-회화-일반회화</t>
+          <t>문화예술-서화-회화</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>세로 : 134 가로 : 54</t>
+          <t>세로 : 100 가로 : 64</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>부부의 초상화 중 남편을 그린 그림. 화폭(세로 91.7, 가로 34). 정자관에 흰색 두루마기를 입고, 서양식 의자에 앉아 있는 모습을 그린 것임. 좌측상단에는 '本貫 永川 壬寅二月初六日 生 李寧澤 影像 辛卯年 漢陽居士 朴松坡'가 묵서됨. 좌측하단에는 낙관 '漢陽居士 朴松坡款'이 찍혀 있음. 전통방식의 초상화를 근대 서양화법으로 제작. 그림용 화견(畵絹)이 아닌 일반옷감에 그렸고, 장황은 종이로 꾸밈. 벽에 걸기 위해 족자 상축에는 2개의 구멍을 뚫고, 실을 엮어 걸 수 있게 만듦. 40455-40456 한 조임.</t>
+          <t>민영휘(閔泳徽, 1852~1935)의 34세 때 초상화. 지본채색(紙本彩色). 화폭(세로 98, 가로62). 청색 단령에 쌍학문 흉배와 각대(角帶), 사모를 착용한 전신 좌상(全身坐像). 화면 왼쪽 상단에 '藥山府伯閔泳駿 時年三十四 乙酉菊月上澣'이 적혀 있음. 영준(泳駿)은 초명임. 민화풍으로 화면 오른쪽에 꽃이 그려져 있음.</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>PS0100200100104045500000</t>
+          <t>PS0100200100103971700000</t>
         </is>
       </c>
       <c r="O78" t="inlineStr"/>
@@ -5851,7 +5855,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>YNFMP04</t>
+          <t>YNFMP07</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5866,19 +5870,23 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>40456</t>
+          <t>45479</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>부부 초상화</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
+          <t>초상</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>肖像</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100104045600000</t>
+          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100104547900000</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5888,7 +5896,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>한국-광복이후</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5898,17 +5906,17 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>세로 : 134 가로 : 54</t>
+          <t>가로 : 75 세로 : 160</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>부부의 초상화 중 부인을 그린 그림. 화폭(세로 91.7, 가로 34). 흰색 저고리와 치마를 입고, 서양식 의자에 앉아 있는 모습을 그린 것임. 좌측상단에는 '本貫 文化 柳氏 丙午十一月 十九日生 辛卯表題畵像'이 묵서됨. 좌측하단에는 낙관 '漢陽居士 朴松坡款'이 찍혀 있음. 전통방식의 초상화를 근대 서양화법으로 제작. 그림용 화견(畵絹)이 아닌 일반 옷감에 그렸고, 장황은 종이로 꾸밈. 벽에 걸기 위해 족자 상축에는 2개의 구멍이 뚫려 있고, 실을 엮어 걸 수 있게 되어 있음. 40455-40456 한 조임.</t>
+          <t>문관(文官)을 그린 그림. 족자. 견본채색(絹本彩色). 화폭(세로 143, 가로 67.7). 쌍학흉배(雙鶴胸背)를 부착한 단령에 사모(紗帽)와 서대(犀帶)를 착용하고 의자에 앉아 있는 전신좌상. 의자에는 호피가, 족좌대(足座臺)에는 화문석이 깔려 있음. 배경에는 소병(素屛)이 배치됨. 화면에 가로·세로로 꺾인 자국이 있고, 안료는 군데군데 박락됨. 화면 우측 상단 한 곳에 구멍이 나 있음. 우측 상단 표장비단 부분에 일부 종이가 붙어 있음. 상축 윗면 좌우 양쪽에 족자 고리 있음.</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>PS0100200100104045600000</t>
+          <t>PS0100200100104547900000</t>
         </is>
       </c>
       <c r="O79" t="inlineStr"/>
@@ -5917,7 +5925,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>YNFMP05</t>
+          <t>YNFMP08</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5932,23 +5940,23 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>40438</t>
+          <t>39716</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>의기 계월향 초상</t>
+          <t>초상</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>義妓 桂月香 肖像</t>
+          <t>肖像</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100104043800000</t>
+          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100103971600000</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5963,22 +5971,22 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>문화예술-서화-회화-일반회화</t>
+          <t>문화예술-서화-회화</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>세로 : 156.5 가로 : 80.6</t>
+          <t>세로 : 116 가로 : 72.5</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>평양 기생 계월향(桂月香·?~1592)을 그린 초상화. 그림 상단에는 '의기 계월향(義妓 桂月香)'이라는 제목의 제발이 적여 있음. 화면(세로 112.0, 가로 61.2) 지본채색(紙本彩色). 머리에는 가채를 쓰고, 녹색 저고리에 치마를 입고, 화문석 위에 앉아 있는 모습을 그림. 왼손에는 검은색 띠를 쥐고 있음</t>
+          <t>흑건(黑巾)에 녹포(綠袍)를 입은 모습의 전신좌상(全身坐像). 족자형. 견본채색(絹本彩色). 화폭(세로 93, 가로 67). 오른손에 홀을 쥐고 있고, 왼손으로는 수염을 만지고 있는 모습임.</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>PS0100200100104043800000</t>
+          <t>PS0100200100103971600000</t>
         </is>
       </c>
       <c r="O80" t="inlineStr"/>
@@ -5987,7 +5995,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>YNFMP06</t>
+          <t>YNFMP16</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6002,23 +6010,23 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>39717</t>
+          <t>45478</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>민영휘 초상</t>
+          <t>조희복 초상</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>閔泳徽 肖像</t>
+          <t>趙羲復肖像</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100103971700000</t>
+          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100104547800000</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6033,22 +6041,22 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>문화예술-서화-회화</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>가로 : 64 세로 : 100</t>
+          <t>가로 : 150 세로 : 98.5</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>민영휘(閔泳徽, 1852~1935)의 34세 때 초상화. 지본채색(紙本彩色). 화폭(세로 98, 가로62). 청색 단령에 쌍학문 흉배와 각대(角帶), 사모를 착용한 전신 좌상(全身坐像). 화면 왼쪽 상단에 '藥山府伯閔泳駿 時年三十四 乙酉菊月上澣'이 적혀 있음. 영준(泳駿)은 초명임. 민화풍으로 화면 오른쪽에 꽃이 그려져 있음.</t>
+          <t>조선 말기 무관 조희복(趙羲復)을 그린 그림. 액자 형태로, 유리가 끼워져 있음. 견본채색(絹本彩色). 화폭(세로 120.5, 가로 77.2). 쌍호흉배(雙虎胸背)를 부착한 단령에 사모(紗帽)와 학정금대(鶴頂金帶)를 착용하고, 부채를 들고 의자에 앉아 있는 전신좌상. 몸체 비례가 맞지 않음. 의자에는 호피가, 족좌대(足座臺)와 바닥에는 화문석이 깔려 있음. 배경에는 일부 접혀있는 산수 병풍이 배치되고, 화면 가장자리에는 테두리가 둘러짐. 좌측 및 하단 일부와 우측 가장자리에 종이가 덧대지고, 우측에는 '判書趙公○羲復之眞影'가 묵서됨. 액자로 개장(改裝)됨. 액자 뒷면 상단부 좌우측에 각각 와이어 고리 달림.</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>PS0100200100103971700000</t>
+          <t>PS0100200100104547800000</t>
         </is>
       </c>
       <c r="O81" t="inlineStr"/>
@@ -6057,7 +6065,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>YNFMP07</t>
+          <t>YNFMP17</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6072,23 +6080,23 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>45479</t>
+          <t>83998</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>초상</t>
+          <t>초상화</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>肖像</t>
+          <t>肖像畵</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100104547900000</t>
+          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100108399800000</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6103,22 +6111,22 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>문화예술-서화-회화-일반회화</t>
+          <t>문화예술-서화-회화</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>세로 : 160 가로 : 75</t>
+          <t>가로 : 67.5 세로 : 113.5</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>문관(文官)을 그린 그림. 족자. 견본채색(絹本彩色). 화폭(세로 143, 가로 67.7). 쌍학흉배(雙鶴胸背)를 부착한 단령에 사모(紗帽)와 서대(犀帶)를 착용하고 의자에 앉아 있는 전신좌상. 의자에는 호피가, 족좌대(足座臺)에는 화문석이 깔려 있음. 배경에는 소병(素屛)이 배치됨. 화면에 가로·세로로 꺾인 자국이 있고, 안료는 군데군데 박락됨. 화면 우측 상단 한 곳에 구멍이 나 있음. 우측 상단 표장비단 부분에 일부 종이가 붙어 있음. 상축 윗면 좌우 양쪽에 족자 고리 있음.</t>
+          <t>화가 석지 채용신(蔡龍臣, 1848-1941)이 그린 초상화(肖像畫). 1919년 작(作). 견본채색(絹本彩色). 산수도(山水圖) 병풍 앞에 가부좌를 한 인물이 그려짐. 인물 오른손에 부채가 들려있고 허리에 달린 호패에 생몰년(生歿年)이 간지로 표현됨. 병풍에는 '己未冬石芝'가 묵서되고 채용신의 낙관(落款)이 찍혀 있음.</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>PS0100200100104547900000</t>
+          <t>PS0100200100108399800000</t>
         </is>
       </c>
       <c r="O82" t="inlineStr"/>
@@ -6127,7 +6135,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>YNFMP08</t>
+          <t>YNFMP28</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6142,23 +6150,23 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>39716</t>
+          <t>40224</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>초상</t>
+          <t>이경하 초상</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>肖像</t>
+          <t>李景夏 肖像</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100103971600000</t>
+          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100104022400000</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6173,22 +6181,22 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>문화예술-서화-회화</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>세로 : 116 가로 : 72.5</t>
+          <t>가로 : 65 세로 : 111.3</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>흑건(黑巾)에 녹포(綠袍)를 입은 모습의 전신좌상(全身坐像). 족자형. 견본채색(絹本彩色). 화폭(세로 93, 가로 67). 오른손에 홀을 쥐고 있고, 왼손으로는 수염을 만지고 있는 모습임.</t>
+          <t>1882년(고종19) 무위대장을 역임한 이경하(李景夏, 1811~1891)의 초상화. 족자형. 견본채색(絹本彩色). 화폭(세로 74, 가로 57.3). 사모에서 흉배까지 그린 반신상. 머리에는 오사모(烏紗帽)를 쓰고, 짙은 녹색을 띤 검정색 운보문단령(雲寶紋團翎)을 입고 있으며, 가슴에는 쌍호흉배를 착용하고, 각대(角帶)를 둘렀음. 우측상단에 신미년(1871)에 쓴 자찬이 쓰여 있고, 백문방인이 찍혀 있음.</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>PS0100200100103971600000</t>
+          <t>PS0100200100104022400000</t>
         </is>
       </c>
       <c r="O83" t="inlineStr"/>
@@ -6197,7 +6205,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>YNFMP09</t>
+          <t>YNFMP29</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6212,23 +6220,23 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>57821</t>
+          <t>81047</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>초상화</t>
+          <t>강현 초상화</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>肖像畵</t>
+          <t>姜鋧 肖像畵</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100105782100000</t>
+          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100108104700000</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6238,7 +6246,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>한국-일제강점</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6248,17 +6256,17 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>가로 : 94.7 세로 : 165.5</t>
+          <t>세로 : 149.5 가로 : 88.5</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>인물의 전신상(全身像)을 그린 그림. 액자 형태. 지본수묵채색(紙本水墨彩色). 화폭(세로 125.6, 가로 75.8). 포와 전복을 입고 정자관을 쓴 인물이 의자에 앉아 있는 모습을 그림.</t>
+          <t>백각 강현(白閣 姜鋧)의 모습을 그린 초상화(肖像畫). 임모본(臨摸本). 액자 형태. 견본채색(絹本彩色). 화폭(세로 115, 가로 72). 쌍학흉배(雙鶴胸背)를 부착한 단령에 사모(紗帽)와 혁대를 착용하고, 두 손을 모으고 의자에 앉아 있는 전신 좌상. 두 발은 족좌대(足座臺)에 올려놓음. 의자에는 호피 둘려있음. 화면 주위는 비단으로 장황(裝潢)됨. 뒷면에 보천교(普天敎) 부적 1개 부착됨.</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>PS0100200100105782100000</t>
+          <t>PS0100200100108104700000</t>
         </is>
       </c>
       <c r="O84" t="inlineStr"/>
@@ -6267,7 +6275,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>YNFMP10</t>
+          <t>YNFMP31</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6282,23 +6290,23 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>47163</t>
+          <t>93350</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>초상</t>
+          <t>한용직 초상화</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>肖像</t>
+          <t>韓用稷 肖像畵</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100104716300000</t>
+          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100109335000000</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6313,22 +6321,22 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>문화예술-서화-회화-일반회화</t>
+          <t>문화예술-서화-회화-기타</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>세로 : 132.3 가로 : 90</t>
+          <t>세로 : 144 가로 : 83</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>정자관(程子冠)에 포(袍)를 입은 남성이 바닥에 화문석 돗자리를 깔고 앉은 부좌상(趺坐像). 액자 형태로, 유리가 끼워져 있음. 견본채색(絹本彩色). 화폭(세로 96, 가로 60). 인물 주위로 문방구류, 서책, 찻잔세트, 머릿장 등이 배치되고, 머릿장이나 나전함, 연대(硯臺) 등의 문양은 세밀하게 표현됨. 액자 뒷면 상단 좌우에 투명 튜브로 감싸진 와이어줄 있음.</t>
+          <t>한용직(韓用稷)을 그린 초상화. 족자형태. 견본채색(絹本彩色). 화폭(세로 121.5, 가로 71). 쌍호 흉배(雙虎 胸背)의 문관복(文官服)을 착용한 인물이 의자에 앉아 있는 전신좌상. 바닥에는 화문석이 깔려 있고 중앙에 인장함(印章函)이 놓여 있음. 좌측 상단에 '三昧抄形全是假七', '分移貌完其真', '門人韓用直謹撰'이 묵서됨. 족자 옆단과 상,하단 비단으로 장황(裝潢)됨. 상단에 유소 2개 늘어뜨림. 반달에 고리 2개가 달리고 족자끈이 연결됨.</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>PS0100200100104716300000</t>
+          <t>PS0100200100109335000000</t>
         </is>
       </c>
       <c r="O85" t="inlineStr"/>
@@ -6337,7 +6345,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>YNFMP11</t>
+          <t>YNFMP32</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6352,23 +6360,23 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>103484</t>
+          <t>99723</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>초상시부조기</t>
+          <t>무관 초상화</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>初喪時扶助記</t>
+          <t>武官肖像畵</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100110348400000</t>
+          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100109972300000</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -6378,27 +6386,27 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>한국-조선</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>사회생활-의례생활-상장-상장문서</t>
+          <t>문화예술-서화-회화-일반회화</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>세로 : 15.5 가로 : 21.1 두께 : 0.4</t>
+          <t>세로 : 144.5 두께 : 6.7 가로 : 67</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>문상객을 기록한 방명록. 1책. 가철(假綴). 필사본(筆寫本). 표지 2장. 내지 6장. 병자년(丙子) 7월 7일 작성. 조문객의 이름과 부의 내용이 기재됨. 초상(初喪)에 참석한 인물이 기재됨.</t>
+          <t>조선시대 무관의 초상을 그린 그림. 양문형 액자에 족자가 걸려 있는 형태. 캔버스(canvas)에 유채. 화면에는 인물의 전신이 배치됨. 3품 이하의 당하관을 상징하는 단호문흉배(單虎紋胸背)가 수(繡) 놓인 녹색 관복과 사모를 착용하고, 등받이가 있는 교의자에 앉아 정면을 응시하고 있는 모습임. 화면 왼쪽 상단에 '崇禎五回甲子淸和節嶺霽權相行謹撰 書'가, 오른쪽 상단에는 '賛日 七分影一幅圖生绡鳥之動色 罒方志六旬齒風采恍若手神 爲袍烏帽認是舊代朝班 彩毫龍眼難畵今日儒迹 仁善爲基 剛倬其志 誰其眞體 吾友晩松'이 적혀 있음. 인물 뒤쪽으로 매작도와 송학도 병풍이 그려짐.</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>PS0100200100110348400000</t>
+          <t>PS0100200100109972300000</t>
         </is>
       </c>
       <c r="O86" t="inlineStr"/>
@@ -6407,7 +6415,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>YNFMP12</t>
+          <t>YNFMP36</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6422,23 +6430,23 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>103730</t>
+          <t>81401</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>초상시집사기</t>
+          <t>문관 초상화</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>初喪時執事記</t>
+          <t>文官 肖像畵</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100110373000000</t>
+          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100108140100000</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6448,27 +6456,27 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>한국-대한제국</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>사회생활-의례생활-제례</t>
+          <t>문화예술-서화-회화-기타</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>가로 : 112.5 세로 : 53.2</t>
+          <t>가로 : 75 세로 : 144</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>집안에서 초상(初喪)을 치를 때 순서와 업무를 분장(分掌) 한 문서. 임오년(壬午) 4월 5월 작성. 호상(護喪), 상례(相禮), 돈장(敦匠), 조빈(造殯), 사서(司書), 사화(司貨)로 나누어 각각 역할과 집사자의 이름이 기재됨.</t>
+          <t>조선 말기 문관을 그린 초상화. 석지(石芝) 채용신(蔡龍臣, 1850~1941) 작(作). 족자형태. 견본채색(絹本彩色). 화폭(세로 113, 가로 66). 단학흉배(單鶴胸背)의 문관복(文官服)을 착용한 인물이 의자에 앉아 있는 전신좌상. 오른손에 부채를 쥐고 있고 허리에 달린 호패에는 '巳酉生(사유생) 癸卯入仕(계묘입사)'가 적혀 있음. 바닥에는 화문석이 깔려 있음. 화면 좌측 중앙에 주문방인(朱文方印)이 찍혀 있음. 화폭 위아래는 장황(裝潢)됨. 상단에 유소 2개 늘어뜨림. 반달에 고리 2개가 달리고 족자끈이 연결됨. 아크릴 액자에 보관됨.</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>PS0100200100110373000000</t>
+          <t>PS0100200100108140100000</t>
         </is>
       </c>
       <c r="O87" t="inlineStr"/>
@@ -6477,7 +6485,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>YNFMP13</t>
+          <t>YNFMP37</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6492,7 +6500,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>37544</t>
+          <t>37543</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6508,7 +6516,7 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100103754400000</t>
+          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100103754300000</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6523,2176 +6531,26 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>미디어-아카이브-사진기록 / 문화예술-서화-회화</t>
+          <t>문화예술-서화-회화-서양화</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>세로 : 29.5 가로 : 23</t>
+          <t>세로 : 72 가로 : 64</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>콧수염을 기르고 검정색 두루마기를 입은 노인의 모습을 그린 영정용 초상화(세로 24, 가로 18). 액자형. 기존 사진에 그림을 덧그려 완성한 형태. 37544-37545 한 조임.</t>
+          <t>문관(文官)복장을 한 남자의 모습을 그린 그림(세로 51, 가로 43.5). 캔버스(canvas)에 유채(油彩). 윤필구(尹弼九) 작(作). 액자형. 화폭 오른쪽에 ‘嘉善大夫竹史徐公之像’이라고 적혀 있음. 그림의 뒷면에 ‘1969. 10. 6 眞影에 依하여 尹弼九 謹寫’, ‘子 丙七’이라고 적혀 있음. 전통 기법으로 그려진 원본을 베껴 유화로 그렸음.</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>PS0100200100103754400000</t>
+          <t>PS0100200100103754300000</t>
         </is>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>YNFMP14</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>103726</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>초상시집사기</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>初喪時執事記</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100110372600000</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>한국</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>사회생활-의례생활-제례</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>세로 : 50 가로 : 88</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>집안에서 초상(初喪)을 치를 때 순서와 업무를 분장(分掌)한 문서. 임진년(壬辰) 1월 7일 작성. 호곡(護哭), 상례(相禮), 축(祝), 진설(陳設), 돈장(敦匠), 조빈(造殯), 사서(司書), 사화(司貨)로 나누어 각각 역할과 집사자의 이름이 기재됨.</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>PS0100200100110372600000</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>YNFMP15</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>37545</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>초상화</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>肖像畫</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100103754500000</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>한국-광복이후</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화 / 미디어-아카이브-사진기록</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>세로 : 29.5 가로 : 23.3</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>'壽'자문이 수 놓여진 두루마기를 입은 여성 노인의 모습을 그린 영정용 초상화(세로 23, 가로 18). 액자형. 기존 사진에 그림을 덧그려 완성한 형태. 37544-37545 한 조임.</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>PS0100200100103754500000</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>YNFMP16</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>45478</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>조희복 초상</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>趙羲復肖像</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100104547800000</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>한국-조선</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-일반회화</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>가로 : 150 세로 : 98.5</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>조선 말기 무관 조희복(趙羲復)을 그린 그림. 액자 형태로, 유리가 끼워져 있음. 견본채색(絹本彩色). 화폭(세로 120.5, 가로 77.2). 쌍호흉배(雙虎胸背)를 부착한 단령에 사모(紗帽)와 학정금대(鶴頂金帶)를 착용하고, 부채를 들고 의자에 앉아 있는 전신좌상. 몸체 비례가 맞지 않음. 의자에는 호피가, 족좌대(足座臺)와 바닥에는 화문석이 깔려 있음. 배경에는 일부 접혀있는 산수 병풍이 배치되고, 화면 가장자리에는 테두리가 둘러짐. 좌측 및 하단 일부와 우측 가장자리에 종이가 덧대지고, 우측에는 '判書趙公○羲復之眞影'가 묵서됨. 액자로 개장(改裝)됨. 액자 뒷면 상단부 좌우측에 각각 와이어 고리 달림.</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>PS0100200100104547800000</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>YNFMP17</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>83998</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>초상화</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>肖像畵</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100108399800000</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>한국-조선</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>세로 : 113.5 가로 : 67.5</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>화가 석지 채용신(蔡龍臣, 1848-1941)이 그린 초상화(肖像畫). 1919년 작(作). 견본채색(絹本彩色). 산수도(山水圖) 병풍 앞에 가부좌를 한 인물이 그려짐. 인물 오른손에 부채가 들려있고 허리에 달린 호패에 생몰년(生歿年)이 간지로 표현됨. 병풍에는 '己未冬石芝'가 묵서되고 채용신의 낙관(落款)이 찍혀 있음.</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>PS0100200100108399800000</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>YNFMP18</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>51676</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>초상화</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>肖像畵</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100105167600000</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>한국-광복이후</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-서양화</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>세로 : 44 가로 : 35.5</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>김언석 부친(김흥태)의 초상화(영정). 1975년 제작. 앞면에 유리가 끼워진 형태. 캔버스(canvas)에 채색. 화폭(세로 38, 가로 29). 캔버스 가장자리를 비단으로 표장(表裝)함. 액자틀 뒷면 상단 중앙에 액자걸이가 달림. 캔버스와 액자틀 옆면과 뒷면에 쇠못이 박힘. 화면 우측 하단에 '75.PARK.S.K' 제작년도와 작가 사인이 적힘.</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>PS0100200100105167600000</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>YNFMP19</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>51677</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>초상화</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>肖像畵</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100105167700000</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>한국-광복이후</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-서양화</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>가로 : 35.5 세로 : 44</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>김언석 모친(박광숙)의 초상화(영정). 1975년 제작. 앞면에 유리가 끼워진 형태. 캔버스(canvas)에 채색. 화폭(세로 38, 가로 29). 캔버스 가장자리를 비단으로 표장(表裝)함. 액자틀 뒷면 상단 중앙에 액자걸이가 달림. 캔버스와 액자틀 옆면과 뒷면에 쇠못이 박힘. 화면 우측 하단에 '75.PARK.S.K' 제작년도와 작가 사인이 적힘.</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>PS0100200100105167700000</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>YNFMP20</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>103710</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>肖像</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100110371000000</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>한국-일제강점</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-일반회화</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>가로 : 60 세로 : 197</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>부부의 초상화 중 남편을 그린 그림. 족자. 견본채색(絹本彩色). 화폭(세로 104.5, 가로 42). 정자관에 흰색 두루마기를 입고, 한 손에 부채를 들고 서양식 의자에 앉아 있는 모습. 좌측 하단에는 '臥牛山人錦島 癸未九月中旬' 묵서되고 낙관(落款) 찍혀 있음. 족자 상하단은 비단으로 장황(裝潢) 됨. 상축 축목에 족자 고리못과 꽃 모양의 고리 장식이 있고, 족자 끈과 유소(流蘇)가 달려 있음.</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>PS0100200100110371000000</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>YNFMP21</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>103711</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>肖像</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100110371100000</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>한국-일제강점</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-일반회화</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>세로 : 197 가로 : 62</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>부부의 초상화 중 부인을 그린 그림. 족자. 견본채색(絹本彩色). 화폭(세로 104.5, 가로 42). 흰색 치마저고리를 입고, 두 손을 모으고 서양식 의자에 앉아 있는 모습. 좌측 하단에는 '臥牛山人錦島 癸未九月中旬' 묵서 되고 낙관(落款) 찍혀 있음. 족자 상하단은 비단으로 장황(裝潢) 됨. 상축 축목에 족자 고리못과 꽃 모양의 고리 장식이 있고, 족자 끈과 유소(流蘇)가 달려 있음.</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>PS0100200100110371100000</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>YNFMP22</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>40459</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>초상화 초본</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>肖像畫 初本</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100104045900000</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>한국-조선</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-일반회화</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>가로 : 53.5 높이 : 85</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>오사모(烏紗帽)에 분홍색 단령(團領)을 입은 반신상 초상화 초본(草本) .액자형. 지본담채(紙本淡彩). 화폭(세로 54, 가로 30). 조선 후기 인물, 강유(姜游)를 그린 그림이라고 전해짐.</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>PS0100200100104045900000</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>YNFMP23</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>78562</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>이명래 초상화 액자</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100107856200000</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>한국-광복이후</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>미디어-아카이브-사진기록-사진</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>세로 : 47.5 가로 : 37.3</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>이명래 선생의 초상화 액자. 직사각 형태로, 앞면에 유리가 끼워짐.</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>PS0100200100107856200000</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>YNFMP24</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>81050</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>차경석 초상화</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>車京石 肖像畵</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100108105000000</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>한국</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-기타</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>세로 : 109 가로 : 73</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>보천교(普天敎)의 창시자인 차경석(車京石)의 모습을 그린 초상화(肖像畵). 지본채색(紙本彩色). 정자관을 쓰고 도포를 입은 차경석이 의자에 앉아있는 모습으로 그려짐. 차경석의 뒤에 병풍이 둘려있음. 좌측 하단에 도장 1과(顆) 찍혀있음.</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>PS0100200100108105000000</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>YNFMP25</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>99725</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>부부 초상화</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>夫婦肖像畵</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100109972500000</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>한국-일제강점</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-일반회화</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>세로 : 58 가로 : 41.5 두께 : 2</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>부부의 모습이 각각 그려진 초상화. 2개의 액자로 구성됨. 종이에 소묘(素描). 화폭(세로47.5, 가로 33). 인물과 잔치상이 묘사됨. 부인의 모습 뒤쪽에 송학도 병풍이 그려지고, 왼쪽 상단에 '拀 昭和十四年二月二十日' 이 적혀 있음.</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>PS0100200100109972500000</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>YNFMP26</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>30875</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>이용익 초상화</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>李容翊肖像畵</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100103087500000</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>한국-대한제국</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>가로 : 111 세로 : 232.5</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>한말(韓末)의 문신이자 정치가인 이용익(李容翊, 1854~1907)의 초상을 그린 그림. 견본채색(絹本彩色). 족자형(세로 312, 가로 124.7). 서양식 제복을 입고 서 있는 모습을 그린 전신초상화(全身肖像畵)임. 가슴에는 3개의 훈장이 달려 있고, 왼손에는 예도(銳刀)를 들고 있음.</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>PS0100200100103087500000</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>YNFMP27</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>송석하 선생 초상화</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100300000100000</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>한국-광복이후</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-서양화</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>가로 : 23 세로 : 32</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>서울대에 다니던 제자가 그려준 송석하 선생의 초상화. 지본채색. 유화. 얼굴은 검은 색 계통으로 전체적인 윤곽만을 강조하였기 때문에 선명하지 못함. 바탕은 녹색 계통임.</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>PS0100200100300000100000</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>YNFMP28</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>40224</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>이경하 초상</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>李景夏 肖像</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100104022400000</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>한국-조선</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-일반회화</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>가로 : 65 세로 : 111.3</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>1882년(고종19) 무위대장을 역임한 이경하(李景夏, 1811~1891)의 초상화. 족자형. 견본채색(絹本彩色). 화폭(세로 74, 가로 57.3). 사모에서 흉배까지 그린 반신상. 머리에는 오사모(烏紗帽)를 쓰고, 짙은 녹색을 띤 검정색 운보문단령(雲寶紋團翎)을 입고 있으며, 가슴에는 쌍호흉배를 착용하고, 각대(角帶)를 둘렀음. 우측상단에 신미년(1871)에 쓴 자찬이 쓰여 있고, 백문방인이 찍혀 있음.</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>PS0100200100104022400000</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>YNFMP29</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>81047</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>강현 초상화</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>姜鋧 肖像畵</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100108104700000</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>한국</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-일반회화</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>세로 : 149.5 가로 : 88.5</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>백각 강현(白閣 姜鋧)의 모습을 그린 초상화(肖像畫). 임모본(臨摸本). 액자 형태. 견본채색(絹本彩色). 화폭(세로 115, 가로 72). 쌍학흉배(雙鶴胸背)를 부착한 단령에 사모(紗帽)와 혁대를 착용하고, 두 손을 모으고 의자에 앉아 있는 전신 좌상. 두 발은 족좌대(足座臺)에 올려놓음. 의자에는 호피 둘려있음. 화면 주위는 비단으로 장황(裝潢)됨. 뒷면에 보천교(普天敎) 부적 1개 부착됨.</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>PS0100200100108104700000</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>YNFMP30</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>70306</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>스님 초상화肖像畵)</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100107030600000</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>한국-조선</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>세로 : 136 가로 : 95.5</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>스님의 모습을 그린 초상화. 액자형태. 견본채색(絹本彩色). 화폭(세로 107.5, 가로 77.5). 화면 중앙에 스님이 결가부좌(結跏趺坐)한 모습이 그려짐. 스님은 녹색의 장삼(長衫)에 홍색 가사(架裟)를 걸치고 주장자(拄杖子)와 염주(念珠)를 들고 있음. 좌측 상단에 ˈ樿敎兩宗觧庵堂信忍之真相ˈ이 묵서되고, 상단 좌우측에 영찬(影讚)이 적혀 있음. 우측 영찬 끝에 주문방인(朱文方印)이 찍혀 있음. 화면 주위는 비단으로 장황(裝潢)됨. 뒷면 상단에 액자 걸이 달림.</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>PS0100200100107030600000</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>YNFMP31</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>93350</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>한용직 초상화</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>韓用稷 肖像畵</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100109335000000</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>한국</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-기타</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>세로 : 144 가로 : 83</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>한용직(韓用稷)을 그린 초상화. 족자형태. 견본채색(絹本彩色). 화폭(세로 121.5, 가로 71). 쌍호 흉배(雙虎 胸背)의 문관복(文官服)을 착용한 인물이 의자에 앉아 있는 전신좌상. 바닥에는 화문석이 깔려 있고 중앙에 인장함(印章函)이 놓여 있음. 좌측 상단에 '三昧抄形全是假七', '分移貌完其真', '門人韓用直謹撰'이 묵서됨. 족자 옆단과 상,하단 비단으로 장황(裝潢)됨. 상단에 유소 2개 늘어뜨림. 반달에 고리 2개가 달리고 족자끈이 연결됨.</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>PS0100200100109335000000</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>YNFMP32</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>99723</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>무관 초상화</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>武官肖像畵</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100109972300000</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>한국-조선</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-일반회화</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>두께 : 6.7 세로 : 144.5 가로 : 67</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>조선시대 무관의 초상을 그린 그림. 양문형 액자에 족자가 걸려 있는 형태. 캔버스(canvas)에 유채. 화면에는 인물의 전신이 배치됨. 3품 이하의 당하관을 상징하는 단호문흉배(單虎紋胸背)가 수(繡) 놓인 녹색 관복과 사모를 착용하고, 등받이가 있는 교의자에 앉아 정면을 응시하고 있는 모습임. 화면 왼쪽 상단에 '崇禎五回甲子淸和節嶺霽權相行謹撰 書'가, 오른쪽 상단에는 '賛日 七分影一幅圖生绡鳥之動色 罒方志六旬齒風采恍若手神 爲袍烏帽認是舊代朝班 彩毫龍眼難畵今日儒迹 仁善爲基 剛倬其志 誰其眞體 吾友晩松'이 적혀 있음. 인물 뒤쪽으로 매작도와 송학도 병풍이 그려짐.</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>PS0100200100109972300000</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>YNFMP33</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>75169</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>김석곤 초상화</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>金晳坤 肖像畵</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100107516900000</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>한국-일제강점</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>세로 : 95 가로 : 66</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>동초 김석곤(東樵 金晳坤)의 모습을 그린 초상화(肖像畫). 석지 채용신(石芝 蔡龍臣, 1848-1941) 작(作). 1918년 제작. 액자 형태. 견본채색(絹本彩色). 화폭(세로 74.5, 가로 46). 산수(山水)를 배경으로, 삿갓을 쓰고 도포(道袍)를 입은 김석곤이 돌 위에 앉아 있는 모습이 그려짐. 좌측 돌 사이에 붓이 그려짐. 우측 상단에 ˈ東樵居士金晳坤笠後肖像ˈ이 묵서되고, 좌측 상단에 1918년(戊午) 김석곤이 쓴 찬(撰)이 있고, ˈ東樵ˈ, ˈ石芝ˈ 등 주문방인(朱門方印) 3과(顆)와 ˈ金晳坤ˈ 등 백문방인(白文方印) 2과가 찍혀 있음. 화면 주위는 비단으로 장황(裝潢)됨.</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>PS0100200100107516900000</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>YNFMP34</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>78854</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>부부 초상화</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100107885400000</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>한국-일제강점</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-일반회화</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>가로 : 120.5 세로 : 140.5</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>조선 말기 화가 채용신(蔡龍臣, 1850~1941) 부부가 의자에 앉은 모습이 묘사된 초상화. 액자 형태. 그림은 족자 형태. 지본채색(紙本彩色). 화폭(세로 120, 가로 102). 좌측에 아내가, 우측에 남편이 그려짐. 아내는 가락지를 낀 왼손을 오른손 위로 포개어 무릎 위에 두고, 남편은 정자관을 쓰고 부채와 안경을 양손에 쥔 모습임. 바닥에 대자리가, 배경에 병풍이 그려짐. 병풍 좌측 하단에 '壬申十二月從二品蔡石芝九十翁寫'가 묵서됨.</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>PS0100200100107885400000</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>YNFMP35</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>39650</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>조철승 초상</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>曺喆承 肖像</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100103965000000</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>한국-일제강점</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>가로 : 91 세로 : 187</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>한의사 조철승(曺喆承, 1849~?)의 42세 때 초상화. 족자형. 견본채색(絹本彩色). 화폭(세로 162, 가로 75). 정자관(程子冠)에 도포를 입고 청색 세조대(細條帶)를 착용한 전신좌상(全身坐像).『잡병제강(雜病堤綱)』이라는 의학서를 오른손에 들고 있음. 이 작품은 원효사 화승(畵僧)인 징헌(登彦)이 경인년(庚寅年:1890년)에 그린 그림을 병진년(丙辰年:1916년)에 최병육(崔丙六)이 다시 모사한 것임. 그림 상단 좌우에 인물에 대한 인적 사항과 그림에 대한 기록이 있음. 인물 주변에 책, 붓 등 문방도 도상이 그려져 있음.</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>PS0100200100103965000000</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>YNFMP36</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>81401</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>문관 초상화</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>文官 肖像畵</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100108140100000</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>한국-대한제국</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-기타</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>가로 : 75 세로 : 144</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>조선 말기 문관을 그린 초상화. 석지(石芝) 채용신(蔡龍臣, 1850~1941) 작(作). 족자형태. 견본채색(絹本彩色). 화폭(세로 113, 가로 66). 단학흉배(單鶴胸背)의 문관복(文官服)을 착용한 인물이 의자에 앉아 있는 전신좌상. 오른손에 부채를 쥐고 있고 허리에 달린 호패에는 '巳酉生(사유생) 癸卯入仕(계묘입사)'가 적혀 있음. 바닥에는 화문석이 깔려 있음. 화면 좌측 중앙에 주문방인(朱文方印)이 찍혀 있음. 화폭 위아래는 장황(裝潢)됨. 상단에 유소 2개 늘어뜨림. 반달에 고리 2개가 달리고 족자끈이 연결됨. 아크릴 액자에 보관됨.</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>PS0100200100108140100000</t>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>YNFMP37</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>37543</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>초상화</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>肖像畫</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100103754300000</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>한국-광복이후</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-서양화</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>가로 : 64 세로 : 72</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>문관(文官)복장을 한 남자의 모습을 그린 그림(세로 51, 가로 43.5). 캔버스(canvas)에 유채(油彩). 윤필구(尹弼九) 작(作). 액자형. 화폭 오른쪽에 ‘嘉善大夫竹史徐公之像’이라고 적혀 있음. 그림의 뒷면에 ‘1969. 10. 6 眞影에 依하여 尹弼九 謹寫’, ‘子 丙七’이라고 적혀 있음. 전통 기법으로 그려진 원본을 베껴 유화로 그렸음.</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>PS0100200100103754300000</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>YNFMP38</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>39654</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>초상화</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>肖像畫</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100103965400000</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>한국-조선</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>세로 : 141 가로 : 81.5</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>정자관(程子冠)에 흰색도포를 입고 녹색 세조대(細條帶)를 두르고 의자에 앉아 있는 전신좌상(全身坐像). 족자형. 마본채색(麻本彩色). 화폭(세로 124, 가로 74.5). 그림 윗부분에는 청색 휘장이, 바닥에는 화문석이 그려져 있음.</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>PS0100200100103965400000</t>
-        </is>
-      </c>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>YNFMP39</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>70307</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>초상화</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>肖像畵</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100107030700000</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>한국-조선</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>세로 : 45.5 가로 : 36.5</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>인물의 얼굴이나 모습을 그린 그림. 액자형태. 견본채색(絹本彩色). 화폭(세로 28, 가로 19). 정자관(程子冠)에 도포를 입고 있는 모습을 그린 반신상(半身像). 상단에 ˈ通政大夫行 承政院 右副承旨兼經筵參贊官繡山申公用珣三十五歲真ˈ이 적혀 있음. 우측 상단에 1895년(乙未)에 적은 찬(撰)이 있고, 백문방인(白文方印)과 주문방인(朱文方印) 이 찍혀 있음. 화면 주위는 비단으로 장황(裝潢)됨. 뒷면 상단 좌우에 액자걸이 부착되고 끈이 달려 있음. 뒷면 하단 좌측에 ˈPeinture coreenne portrait dˈun mandarin collection Collin de Plancyˈ이 적혀 있음.</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>PS0100200100107030700000</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>YNFMP40</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>45862</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>윤씨조모초상</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>尹氏祖母肖像</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100104586200000</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>한국-일제강점</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-일반회화</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>가로 : 58 세로 : 118</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>윤씨조모(尹氏祖母)를 그린 그림. 석지 채용신(石芝 蔡龍臣, 1850~1941) 작(作). 족자. 견본채색(絹本彩色). 화폭(세로 98.5, 가로 54.6). 3폭의 산수 병풍을 배경으로, '壽'자문이 그려진 흰색 치마저고리를 입고, 가슴에는 노리개와 단도를 달고 있는 전신좌상. 얼굴, 머리, 목 부분은 종이를 덧붙인 후 그려지고, 손에는 일부 수정 흔적 있음. 족자 상하단은 비단으로 표장(表裝)됨. 상축에 족자고리못과 꽃모양의 고리장식이 있고, 족자끈과 유소(流蘇)가 달려 있음. 뒷면 좌측 상단에 '甲寅年生尹氏祖母象 石芝蔡龍臣'이 묵서된 붉은색 별지가 붙어 있고, 보호지로 덮여 있음.</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>PS0100200100104586200000</t>
-        </is>
-      </c>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>YNFMP41</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>15295</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>조씨삼형제 초상</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>趙氏三兄弟 肖像</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100101529500000</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>한국-조선</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-일반회화</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>가로 : 66.5 세로 : 42</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>평양조씨(平壤趙氏) 집안의 첫째 조계(趙啓 - '啓'字의 '口'대신 '山'이 들어간 글자를 만들어 사용함), 둘째 조두(趙㞳), 셋째 조강(趙岡) 삼형제를 그린 그림임.</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>PS0100200100101529500000</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>YNFMP42</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>63742</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>강일순 초상화</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>姜一淳肖像畵</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100106374200000</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>한국</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>종교신앙</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>가로 : 132.5 세로 : 147</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>증산교(甑山敎) 창시자 강일순(姜一淳, 1871~1909)을 그린 그림. 종이에 사직(絲織)을 붙이고 그 위에 그림을 그린 형태. 도포를 입고 5층 정자관을 쓴 인물이 연꽃 대좌에 서 있음. 광배와 백호(白毫)가 있음. 오른손은 엄지와 검지를, 왼손은 엄지와 중지를 붙인 형태의 수인(手印)을 하고 있음. 인물 양측에 목패가 있음.</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>PS0100200100106374200000</t>
-        </is>
-      </c>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>YNFMP43</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>78327</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>유진오 초상화</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100107832700000</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>한국-광복이후</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-서양화</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>세로 : 27.3 가로 : 24.2</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>움직이는 사람이나 사물의 형태를 빠르게 그린 그림. 현민 유진오(玄民 兪鎭午)의 얼굴임.</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>PS0100200100107832700000</t>
-        </is>
-      </c>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>YNFMP44</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>초상</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>국립민속박물관</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>37540</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>추수초상</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>秋水肖像</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>https://www.nfm.go.kr/user/data/home/101/DataRelicView.do?seq=PS0100200100103754000000</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>전윤우</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>한국-일제강점</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>문화예술-서화-회화-일반회화</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>가로 : 73 세로 : 113.5 두께 : 7.5</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>추수(秋水) 김제덕(金濟悳, 1855~1925)의 초상화(세로 89, 가로 59). 비단에 채색. 석지(石芝) 채용신(蔡龍臣, 1850~1941) 작(作). 화폭 우측 상단에 ' 秋水翁六十七歲像', 좌측 하단에 '一千○十五萬五千八百三十八年辛酉小春上澣從二品前府使石芝八十翁寫'라고 적혀 있음. 영정은 표구되어 문이 달린 함에 보관됨. 함의 위 아래 머름칸에는 여의두문이 장식되고 문종이에는 국화문이 그려짐.</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>PS0100200100103754000000</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
